--- a/processed_output/DivisionMapping.xlsx
+++ b/processed_output/DivisionMapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2100"/>
+  <dimension ref="A1:B3055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21506,6 +21506,9636 @@
         <v>2099</v>
       </c>
     </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>(out of district of columbia funds)</t>
+        </is>
+      </c>
+      <c r="B2101" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>(out of postal fund)</t>
+        </is>
+      </c>
+      <c r="B2102" t="n">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>1967 economic censuses</t>
+        </is>
+      </c>
+      <c r="B2103" t="n">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>1972 census of governments</t>
+        </is>
+      </c>
+      <c r="B2104" t="n">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>administrative conference of the united states</t>
+        </is>
+      </c>
+      <c r="B2105" t="n">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>administrative expenses, low rent public housing</t>
+        </is>
+      </c>
+      <c r="B2106" t="n">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>administrative provisions, health services and mental health administration</t>
+        </is>
+      </c>
+      <c r="B2107" t="n">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>agricultural conservation program</t>
+        </is>
+      </c>
+      <c r="B2108" t="n">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>alaska housing</t>
+        </is>
+      </c>
+      <c r="B2109" t="n">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>alaska power administration</t>
+        </is>
+      </c>
+      <c r="B2110" t="n">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>allowances and office staff for former presidents</t>
+        </is>
+      </c>
+      <c r="B2111" t="n">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>american revolution bicentennial commission</t>
+        </is>
+      </c>
+      <c r="B2112" t="n">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>anadromous and great lakes fisheries conservation</t>
+        </is>
+      </c>
+      <c r="B2113" t="n">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>appalachian regional development programs</t>
+        </is>
+      </c>
+      <c r="B2114" t="n">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>atlantic-pacific interoceanic canal study commission</t>
+        </is>
+      </c>
+      <c r="B2115" t="n">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>bridge alterations</t>
+        </is>
+      </c>
+      <c r="B2116" t="n">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>building occupancy</t>
+        </is>
+      </c>
+      <c r="B2117" t="n">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>bureau of narcotics and dangerous drugs</t>
+        </is>
+      </c>
+      <c r="B2118" t="n">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>bureau of public roads, limitation on general expenses</t>
+        </is>
+      </c>
+      <c r="B2119" t="n">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>bureau of railroad safety</t>
+        </is>
+      </c>
+      <c r="B2120" t="n">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>business loan and investment fund
+ disaster loan fund</t>
+        </is>
+      </c>
+      <c r="B2121" t="n">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>chamizal memorial highway</t>
+        </is>
+      </c>
+      <c r="B2122" t="n">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>check forgery insurance fund</t>
+        </is>
+      </c>
+      <c r="B2123" t="n">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>civil rights education</t>
+        </is>
+      </c>
+      <c r="B2124" t="n">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>college housing</t>
+        </is>
+      </c>
+      <c r="B2125" t="n">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>colorado river basin project</t>
+        </is>
+      </c>
+      <c r="B2126" t="n">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>commission on obscenity and pornography</t>
+        </is>
+      </c>
+      <c r="B2127" t="n">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>community development training programs</t>
+        </is>
+      </c>
+      <c r="B2128" t="n">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>comprehensive planning grants</t>
+        </is>
+      </c>
+      <c r="B2129" t="n">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>consolidation of departmental headquarters</t>
+        </is>
+      </c>
+      <c r="B2130" t="n">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>construction and maintenance</t>
+        </is>
+      </c>
+      <c r="B2131" t="n">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>construction grants for waste treatment works</t>
+        </is>
+      </c>
+      <c r="B2132" t="n">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>construction of headquarters facility</t>
+        </is>
+      </c>
+      <c r="B2133" t="n">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>construction of secret service training facilities</t>
+        </is>
+      </c>
+      <c r="B2134" t="n">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>construction, national capital airports</t>
+        </is>
+      </c>
+      <c r="B2135" t="n">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>consumer and marketing service</t>
+        </is>
+      </c>
+      <c r="B2136" t="n">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>consumer protective, marketing, and regulatory programs</t>
+        </is>
+      </c>
+      <c r="B2137" t="n">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>cooperative state research service</t>
+        </is>
+      </c>
+      <c r="B2138" t="n">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>court of appeals, district courts, and other
+ judicial services</t>
+        </is>
+      </c>
+      <c r="B2139" t="n">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>court of military appeals, defense</t>
+        </is>
+      </c>
+      <c r="B2140" t="n">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>cropland adjustment program</t>
+        </is>
+      </c>
+      <c r="B2141" t="n">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>current authorizations out of general funds</t>
+        </is>
+      </c>
+      <c r="B2142" t="n">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>defense mobilization functions of federal agencies</t>
+        </is>
+      </c>
+      <c r="B2143" t="n">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>demonstrations and intergovernmental relations</t>
+        </is>
+      </c>
+      <c r="B2144" t="n">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>depaetment of health, education, and welfare</t>
+        </is>
+      </c>
+      <c r="B2145" t="n">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>department of defense—military
+ military personnel</t>
+        </is>
+      </c>
+      <c r="B2146" t="n">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>department of health, education, and welfare
+ office of education</t>
+        </is>
+      </c>
+      <c r="B2147" t="n">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>department of health, education, and welfare health services and mental health administration</t>
+        </is>
+      </c>
+      <c r="B2148" t="n">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>department of housing and urban development</t>
+        </is>
+      </c>
+      <c r="B2149" t="n">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>department of the army
+ corps of engineers—civil</t>
+        </is>
+      </c>
+      <c r="B2150" t="n">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>department of the army
+ corps or engineers—civil</t>
+        </is>
+      </c>
+      <c r="B2151" t="n">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>department of transportation</t>
+        </is>
+      </c>
+      <c r="B2152" t="n">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>deserve personnel, navy</t>
+        </is>
+      </c>
+      <c r="B2153" t="n">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>development facilities</t>
+        </is>
+      </c>
+      <c r="B2154" t="n">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>disease prevention and environmental control</t>
+        </is>
+      </c>
+      <c r="B2155" t="n">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>district of columbia medical facilities</t>
+        </is>
+      </c>
+      <c r="B2156" t="n">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>economic development assistance</t>
+        </is>
+      </c>
+      <c r="B2157" t="n">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>economic research service</t>
+        </is>
+      </c>
+      <c r="B2158" t="n">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>emergency conservation measures</t>
+        </is>
+      </c>
+      <c r="B2159" t="n">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>emergency credit revolving fund</t>
+        </is>
+      </c>
+      <c r="B2160" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>emergency credit revolving fund (disaster loans)</t>
+        </is>
+      </c>
+      <c r="B2161" t="n">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>emergency health</t>
+        </is>
+      </c>
+      <c r="B2162" t="n">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>environmental science services administration</t>
+        </is>
+      </c>
+      <c r="B2163" t="n">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>expenses, agricultural stabilization and conservation service</t>
+        </is>
+      </c>
+      <c r="B2164" t="n">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>facilities, equipment, and construction</t>
+        </is>
+      </c>
+      <c r="B2165" t="n">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>farmer cooperative service</t>
+        </is>
+      </c>
+      <c r="B2166" t="n">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>federal aid for commercial fisheries research and development</t>
+        </is>
+      </c>
+      <c r="B2167" t="n">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>federal aviation administration</t>
+        </is>
+      </c>
+      <c r="B2168" t="n">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>federal contribution</t>
+        </is>
+      </c>
+      <c r="B2169" t="n">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>federal field committee for development planning in alaska</t>
+        </is>
+      </c>
+      <c r="B2170" t="n">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>federal highway administration</t>
+        </is>
+      </c>
+      <c r="B2171" t="n">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>federal insurance administration</t>
+        </is>
+      </c>
+      <c r="B2172" t="n">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>federal law enforcement training center</t>
+        </is>
+      </c>
+      <c r="B2173" t="n">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>federal payment to the district of columbia</t>
+        </is>
+      </c>
+      <c r="B2174" t="n">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>federal railroad administration</t>
+        </is>
+      </c>
+      <c r="B2175" t="n">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>federal water pollution control administration</t>
+        </is>
+      </c>
+      <c r="B2176" t="n">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>fees and expenses of court-appointed counsel</t>
+        </is>
+      </c>
+      <c r="B2177" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>fellowships for city planning and urban studies</t>
+        </is>
+      </c>
+      <c r="B2178" t="n">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>fishermen’s protective fund</t>
+        </is>
+      </c>
+      <c r="B2179" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>flood insurance</t>
+        </is>
+      </c>
+      <c r="B2180" t="n">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>food stamp program</t>
+        </is>
+      </c>
+      <c r="B2181" t="n">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>foreign direct investment control</t>
+        </is>
+      </c>
+      <c r="B2182" t="n">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>general provisions—civil defense</t>
+        </is>
+      </c>
+      <c r="B2183" t="n">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>general provisions—department of the interior</t>
+        </is>
+      </c>
+      <c r="B2184" t="n">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>government payment for annuitants, employees health benefits</t>
+        </is>
+      </c>
+      <c r="B2185" t="n">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>grants for basic water and sewer facilities</t>
+        </is>
+      </c>
+      <c r="B2186" t="n">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>grants for construction of state nursing homes</t>
+        </is>
+      </c>
+      <c r="B2187" t="n">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>grants for neighborhood facilities</t>
+        </is>
+      </c>
+      <c r="B2188" t="n">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>grants to aid advance acquisition of land</t>
+        </is>
+      </c>
+      <c r="B2189" t="n">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>great plains conservation program</t>
+        </is>
+      </c>
+      <c r="B2190" t="n">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>health manpower</t>
+        </is>
+      </c>
+      <c r="B2191" t="n">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>health services</t>
+        </is>
+      </c>
+      <c r="B2192" t="n">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>high-speed ground transportation research and development</t>
+        </is>
+      </c>
+      <c r="B2193" t="n">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>higher educational activities</t>
+        </is>
+      </c>
+      <c r="B2194" t="n">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>highway beautification (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2195" t="n">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>highway trust fund</t>
+        </is>
+      </c>
+      <c r="B2196" t="n">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>homeownership and rental housing assistance</t>
+        </is>
+      </c>
+      <c r="B2197" t="n">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>indemnity payments to dairy farmers</t>
+        </is>
+      </c>
+      <c r="B2198" t="n">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>independent offices
+ appalachian regional commission</t>
+        </is>
+      </c>
+      <c r="B2199" t="n">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>industrial development loans and guarantees</t>
+        </is>
+      </c>
+      <c r="B2200" t="n">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>international financial institutions</t>
+        </is>
+      </c>
+      <c r="B2201" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>land and water conservation</t>
+        </is>
+      </c>
+      <c r="B2202" t="n">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>law enforcement assistance administration</t>
+        </is>
+      </c>
+      <c r="B2203" t="n">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>lewis and clark trail commission</t>
+        </is>
+      </c>
+      <c r="B2204" t="n">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>limitation on administrative and nonadministrative expenses, federal home loan bank board</t>
+        </is>
+      </c>
+      <c r="B2205" t="n">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>limitation on administrative expenses, college housing loans</t>
+        </is>
+      </c>
+      <c r="B2206" t="n">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>limitation on administrative expenses, government national mortgage association</t>
+        </is>
+      </c>
+      <c r="B2207" t="n">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>limitation on administrative expenses, housing for the elderly or handicapped</t>
+        </is>
+      </c>
+      <c r="B2208" t="n">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>limitation on administrative expenses, public facility loans</t>
+        </is>
+      </c>
+      <c r="B2209" t="n">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>limitation on administrative expenses, revolving fund (liquidating programs)</t>
+        </is>
+      </c>
+      <c r="B2210" t="n">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>low and moderate income sponsor fund</t>
+        </is>
+      </c>
+      <c r="B2211" t="n">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>low rent public housing annual contributions</t>
+        </is>
+      </c>
+      <c r="B2212" t="n">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>members’ clerk hike</t>
+        </is>
+      </c>
+      <c r="B2213" t="n">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>metropolitan development</t>
+        </is>
+      </c>
+      <c r="B2214" t="n">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>minority business enterprise</t>
+        </is>
+      </c>
+      <c r="B2215" t="n">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>model cities and governmental relations</t>
+        </is>
+      </c>
+      <c r="B2216" t="n">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>model cities programs</t>
+        </is>
+      </c>
+      <c r="B2217" t="n">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>mortgage credit</t>
+        </is>
+      </c>
+      <c r="B2218" t="n">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>motor carrier safety</t>
+        </is>
+      </c>
+      <c r="B2219" t="n">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>museum programs and related research (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2220" t="n">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>mutual and self-help housing</t>
+        </is>
+      </c>
+      <c r="B2221" t="n">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>national agricultural library</t>
+        </is>
+      </c>
+      <c r="B2222" t="n">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>national commission on product safety</t>
+        </is>
+      </c>
+      <c r="B2223" t="n">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>national commission on reform of federal criminal laws</t>
+        </is>
+      </c>
+      <c r="B2224" t="n">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>national council on marine resources and engineering development</t>
+        </is>
+      </c>
+      <c r="B2225" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>national foundation on the arts and the humanities</t>
+        </is>
+      </c>
+      <c r="B2226" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>national historical publications grants</t>
+        </is>
+      </c>
+      <c r="B2227" t="n">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>national transportation safety board
+ salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2228" t="n">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>national water commission</t>
+        </is>
+      </c>
+      <c r="B2229" t="n">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>new community assistance</t>
+        </is>
+      </c>
+      <c r="B2230" t="n">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>nineteenth decennial census</t>
+        </is>
+      </c>
+      <c r="B2231" t="n">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>office of emergency preparedness</t>
+        </is>
+      </c>
+      <c r="B2232" t="n">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>office of management services</t>
+        </is>
+      </c>
+      <c r="B2233" t="n">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>office of state technical services</t>
+        </is>
+      </c>
+      <c r="B2234" t="n">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>office of the administrator, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2235" t="n">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>office of the surgeon general</t>
+        </is>
+      </c>
+      <c r="B2236" t="n">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>office of the surgeon general
+ comprehensive health planning and services</t>
+        </is>
+      </c>
+      <c r="B2237" t="n">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>office of the territories</t>
+        </is>
+      </c>
+      <c r="B2238" t="n">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>office of water resources research</t>
+        </is>
+      </c>
+      <c r="B2239" t="n">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>open space land programs</t>
+        </is>
+      </c>
+      <c r="B2240" t="n">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>operating expenses, executive mansion</t>
+        </is>
+      </c>
+      <c r="B2241" t="n">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>operating expenses, property management and disposal service</t>
+        </is>
+      </c>
+      <c r="B2242" t="n">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>operation and maintenance, national capital airports</t>
+        </is>
+      </c>
+      <c r="B2243" t="n">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>other independent agencies</t>
+        </is>
+      </c>
+      <c r="B2244" t="n">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>other public health service</t>
+        </is>
+      </c>
+      <c r="B2245" t="n">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>packers and stockyards administration</t>
+        </is>
+      </c>
+      <c r="B2246" t="n">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>panama canal company fund</t>
+        </is>
+      </c>
+      <c r="B2247" t="n">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>parkway and road construction (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2248" t="n">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>payment to fishermen’s protective fund</t>
+        </is>
+      </c>
+      <c r="B2249" t="n">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>payments and expenses</t>
+        </is>
+      </c>
+      <c r="B2250" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>payments to states and possessions</t>
+        </is>
+      </c>
+      <c r="B2251" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>planning, technical assistance, and research</t>
+        </is>
+      </c>
+      <c r="B2252" t="n">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>pollution control operations and research</t>
+        </is>
+      </c>
+      <c r="B2253" t="n">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>postal public buildings</t>
+        </is>
+      </c>
+      <c r="B2254" t="n">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>preservation of historic properties</t>
+        </is>
+      </c>
+      <c r="B2255" t="n">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B2256" t="n">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>public land law review commission</t>
+        </is>
+      </c>
+      <c r="B2257" t="n">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>railroad research</t>
+        </is>
+      </c>
+      <c r="B2258" t="n">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>regional management and services</t>
+        </is>
+      </c>
+      <c r="B2259" t="n">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>removal of surplus agricultural commodities (section 32)</t>
+        </is>
+      </c>
+      <c r="B2260" t="n">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>renewal and housing assistance</t>
+        </is>
+      </c>
+      <c r="B2261" t="n">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>rent supplement program</t>
+        </is>
+      </c>
+      <c r="B2262" t="n">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>repair and improvement or public buildings</t>
+        </is>
+      </c>
+      <c r="B2263" t="n">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>research, development, test and evaluation</t>
+        </is>
+      </c>
+      <c r="B2264" t="n">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>resource conservation and development</t>
+        </is>
+      </c>
+      <c r="B2265" t="n">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>restoration and renovation of buildings</t>
+        </is>
+      </c>
+      <c r="B2266" t="n">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>right-of-way revolver; fund (liquidation of contract authorization) (trust fund)</t>
+        </is>
+      </c>
+      <c r="B2267" t="n">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>river basin surveys and investigations</t>
+        </is>
+      </c>
+      <c r="B2268" t="n">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>rural community development service</t>
+        </is>
+      </c>
+      <c r="B2269" t="n">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>rural housing direct loan account</t>
+        </is>
+      </c>
+      <c r="B2270" t="n">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>rural housing for domestic farm labor</t>
+        </is>
+      </c>
+      <c r="B2271" t="n">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>rural water and waste disposal grants</t>
+        </is>
+      </c>
+      <c r="B2272" t="n">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>salaries and expenses, telecommunications</t>
+        </is>
+      </c>
+      <c r="B2273" t="n">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>salaries, officers, and employees</t>
+        </is>
+      </c>
+      <c r="B2274" t="n">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>saline water conversion</t>
+        </is>
+      </c>
+      <c r="B2275" t="n">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>satellite operations</t>
+        </is>
+      </c>
+      <c r="B2276" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>scientific activities (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2277" t="n">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>self-help housing land development fund</t>
+        </is>
+      </c>
+      <c r="B2278" t="n">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>social and rehabilitation service</t>
+        </is>
+      </c>
+      <c r="B2279" t="n">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>special milk program</t>
+        </is>
+      </c>
+      <c r="B2280" t="n">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>state and community highway safety (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2281" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>subscription to capital stock</t>
+        </is>
+      </c>
+      <c r="B2282" t="n">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>supplies and services</t>
+        </is>
+      </c>
+      <c r="B2283" t="n">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>traffic and highway safety</t>
+        </is>
+      </c>
+      <c r="B2284" t="n">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>transportation planning, research, and development</t>
+        </is>
+      </c>
+      <c r="B2285" t="n">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>u.s. secret service</t>
+        </is>
+      </c>
+      <c r="B2286" t="n">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>urban mass transportation administration</t>
+        </is>
+      </c>
+      <c r="B2287" t="n">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>urban mass transportation fund</t>
+        </is>
+      </c>
+      <c r="B2288" t="n">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>urban renewal programs</t>
+        </is>
+      </c>
+      <c r="B2289" t="n">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>urban research and technology</t>
+        </is>
+      </c>
+      <c r="B2290" t="n">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>urban technology and research</t>
+        </is>
+      </c>
+      <c r="B2291" t="n">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>vessels</t>
+        </is>
+      </c>
+      <c r="B2292" t="n">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>wage and labor standards
+ bureau of employees’ compensation</t>
+        </is>
+      </c>
+      <c r="B2293" t="n">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>wage and labor standards administration</t>
+        </is>
+      </c>
+      <c r="B2294" t="n">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>water resources council</t>
+        </is>
+      </c>
+      <c r="B2295" t="n">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>water resources planning</t>
+        </is>
+      </c>
+      <c r="B2296" t="n">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>watershed planning</t>
+        </is>
+      </c>
+      <c r="B2297" t="n">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>watershed works of improvement</t>
+        </is>
+      </c>
+      <c r="B2298" t="n">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>(our of the postal fund)</t>
+        </is>
+      </c>
+      <c r="B2299" t="n">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>aerospace defense command</t>
+        </is>
+      </c>
+      <c r="B2300" t="n">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>air pollution control</t>
+        </is>
+      </c>
+      <c r="B2301" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>army medical department</t>
+        </is>
+      </c>
+      <c r="B2302" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>asian development bank</t>
+        </is>
+      </c>
+      <c r="B2303" t="n">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>atlantic ocean area</t>
+        </is>
+      </c>
+      <c r="B2304" t="n">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>bureau of apprenticeship and training, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2305" t="n">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>bureau of employment security, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2306" t="n">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>cabinet committee on opportunities for spanish-speaking people</t>
+        </is>
+      </c>
+      <c r="B2307" t="n">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>civil service commission
+ federal labor relations council</t>
+        </is>
+      </c>
+      <c r="B2308" t="n">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>commission on government procurement</t>
+        </is>
+      </c>
+      <c r="B2309" t="n">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>commission on population growth and the american future</t>
+        </is>
+      </c>
+      <c r="B2310" t="n">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>communicable diseases</t>
+        </is>
+      </c>
+      <c r="B2311" t="n">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>community development training and urban fellowship programs</t>
+        </is>
+      </c>
+      <c r="B2312" t="n">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>comprehensive health planning and services</t>
+        </is>
+      </c>
+      <c r="B2313" t="n">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>construction of health educational, research, and library facilities</t>
+        </is>
+      </c>
+      <c r="B2314" t="n">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>consumer protection and environmental health service</t>
+        </is>
+      </c>
+      <c r="B2315" t="n">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>cooperative extension work, payments, and expenses</t>
+        </is>
+      </c>
+      <c r="B2316" t="n">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>dental health</t>
+        </is>
+      </c>
+      <c r="B2317" t="n">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>department oe justice</t>
+        </is>
+      </c>
+      <c r="B2318" t="n">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>department of health, education, and welfare
+ health services and mental health administration</t>
+        </is>
+      </c>
+      <c r="B2319" t="n">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>development of programs for the aging</t>
+        </is>
+      </c>
+      <c r="B2320" t="n">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>economic opportunity program</t>
+        </is>
+      </c>
+      <c r="B2321" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>education in foreign languages and world affairs</t>
+        </is>
+      </c>
+      <c r="B2322" t="n">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>education professions development</t>
+        </is>
+      </c>
+      <c r="B2323" t="n">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>eighth naval district</t>
+        </is>
+      </c>
+      <c r="B2324" t="n">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>elementary and secondary education</t>
+        </is>
+      </c>
+      <c r="B2325" t="n">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>eleventh naval district</t>
+        </is>
+      </c>
+      <c r="B2326" t="n">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>environmental con frol</t>
+        </is>
+      </c>
+      <c r="B2327" t="n">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>environmental control</t>
+        </is>
+      </c>
+      <c r="B2328" t="n">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>environmental health service</t>
+        </is>
+      </c>
+      <c r="B2329" t="n">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>european area</t>
+        </is>
+      </c>
+      <c r="B2330" t="n">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>export-import bank of the united states</t>
+        </is>
+      </c>
+      <c r="B2331" t="n">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>federal chop insurance corporation</t>
+        </is>
+      </c>
+      <c r="B2332" t="n">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>federal contract compliance and civil rights program</t>
+        </is>
+      </c>
+      <c r="B2333" t="n">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>federal home wan bank board</t>
+        </is>
+      </c>
+      <c r="B2334" t="n">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>federal labor relations council, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2335" t="n">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>federal metal and nonmetallic mine safety board of review</t>
+        </is>
+      </c>
+      <c r="B2336" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>federal radiation council</t>
+        </is>
+      </c>
+      <c r="B2337" t="n">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>fifth naval district</t>
+        </is>
+      </c>
+      <c r="B2338" t="n">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>first naval district</t>
+        </is>
+      </c>
+      <c r="B2339" t="n">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>food and drug control</t>
+        </is>
+      </c>
+      <c r="B2340" t="n">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>foreign assistance: economic assistance</t>
+        </is>
+      </c>
+      <c r="B2341" t="n">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>foreign military credit sales</t>
+        </is>
+      </c>
+      <c r="B2342" t="n">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>forest roads and trails (liquidation of contract authority)</t>
+        </is>
+      </c>
+      <c r="B2343" t="n">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>fourteenth naval district</t>
+        </is>
+      </c>
+      <c r="B2344" t="n">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>fourth naval district</t>
+        </is>
+      </c>
+      <c r="B2345" t="n">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>funds appropriated to the president
+ international financial institution</t>
+        </is>
+      </c>
+      <c r="B2346" t="n">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>general research and service</t>
+        </is>
+      </c>
+      <c r="B2347" t="n">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>general services administration
+ real property activities</t>
+        </is>
+      </c>
+      <c r="B2348" t="n">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>government payments for annuitants, employees health benefits</t>
+        </is>
+      </c>
+      <c r="B2349" t="n">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>grants for rehabilitation services and facilities</t>
+        </is>
+      </c>
+      <c r="B2350" t="n">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>health education loans</t>
+        </is>
+      </c>
+      <c r="B2351" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>health services and mental health administration</t>
+        </is>
+      </c>
+      <c r="B2352" t="n">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>health services research and development</t>
+        </is>
+      </c>
+      <c r="B2353" t="n">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>higher education facilities loan fund</t>
+        </is>
+      </c>
+      <c r="B2354" t="n">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>hospital construction</t>
+        </is>
+      </c>
+      <c r="B2355" t="n">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>howard university
+ construction</t>
+        </is>
+      </c>
+      <c r="B2356" t="n">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>human resources</t>
+        </is>
+      </c>
+      <c r="B2357" t="n">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>increase in quota, international monetary fund</t>
+        </is>
+      </c>
+      <c r="B2358" t="n">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>instructional equipment</t>
+        </is>
+      </c>
+      <c r="B2359" t="n">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>inter-agency committee on mexican-american affairs</t>
+        </is>
+      </c>
+      <c r="B2360" t="n">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>inter-american social development institute</t>
+        </is>
+      </c>
+      <c r="B2361" t="n">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>interest adjustment payments</t>
+        </is>
+      </c>
+      <c r="B2362" t="n">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>intergovernmental agencies</t>
+        </is>
+      </c>
+      <c r="B2363" t="n">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>international monetary fund</t>
+        </is>
+      </c>
+      <c r="B2364" t="n">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>international organizations and conference</t>
+        </is>
+      </c>
+      <c r="B2365" t="n">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>investment in interamerican development bank</t>
+        </is>
+      </c>
+      <c r="B2366" t="n">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>john e. fogarty international center for advanced study in the health sciences</t>
+        </is>
+      </c>
+      <c r="B2367" t="n">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>juvenile delinquency prevention and control</t>
+        </is>
+      </c>
+      <c r="B2368" t="n">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>labor-management services administration, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2369" t="n">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>libraries and community services</t>
+        </is>
+      </c>
+      <c r="B2370" t="n">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>limitation on administrate expenses, revolving fund (liquidating programs)</t>
+        </is>
+      </c>
+      <c r="B2371" t="n">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>limitation on administrative. expenses</t>
+        </is>
+      </c>
+      <c r="B2372" t="n">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>limitation on construction</t>
+        </is>
+      </c>
+      <c r="B2373" t="n">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>limitation on program activity</t>
+        </is>
+      </c>
+      <c r="B2374" t="n">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>limitation on unemployment insurance service, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2375" t="n">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>loans to the district of columbia for capital outlay</t>
+        </is>
+      </c>
+      <c r="B2376" t="n">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>low rent public housing</t>
+        </is>
+      </c>
+      <c r="B2377" t="n">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>manpower administration, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2378" t="n">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>manpower training activities</t>
+        </is>
+      </c>
+      <c r="B2379" t="n">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>maternal and child health</t>
+        </is>
+      </c>
+      <c r="B2380" t="n">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>maternal and child health and welfare</t>
+        </is>
+      </c>
+      <c r="B2381" t="n">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>medical facilities construction</t>
+        </is>
+      </c>
+      <c r="B2382" t="n">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>mental health</t>
+        </is>
+      </c>
+      <c r="B2383" t="n">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>mental retardation</t>
+        </is>
+      </c>
+      <c r="B2384" t="n">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>military airlift command</t>
+        </is>
+      </c>
+      <c r="B2385" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>military traffic management and terminal service</t>
+        </is>
+      </c>
+      <c r="B2386" t="n">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>model secondary school for the deaf</t>
+        </is>
+      </c>
+      <c r="B2387" t="n">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>mortgage credit
+ federal housing administration</t>
+        </is>
+      </c>
+      <c r="B2388" t="n">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>national commission on consumer finance</t>
+        </is>
+      </c>
+      <c r="B2389" t="n">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>national council on indian opportunity</t>
+        </is>
+      </c>
+      <c r="B2390" t="n">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>national heart and lung institute</t>
+        </is>
+      </c>
+      <c r="B2391" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>national institute of neurological diseases and stroke</t>
+        </is>
+      </c>
+      <c r="B2392" t="n">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>national, library of medicine</t>
+        </is>
+      </c>
+      <c r="B2393" t="n">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>naval district washington</t>
+        </is>
+      </c>
+      <c r="B2394" t="n">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>ninth naval district</t>
+        </is>
+      </c>
+      <c r="B2395" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>office for civil rights, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2396" t="n">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>office of administration, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2397" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>office of child development</t>
+        </is>
+      </c>
+      <c r="B2398" t="n">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>office of community and field services, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2399" t="n">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>office of economic opportunity</t>
+        </is>
+      </c>
+      <c r="B2400" t="n">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>office of federal contract compliance and civil rights program</t>
+        </is>
+      </c>
+      <c r="B2401" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>office of manpower administrator, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2402" t="n">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>office of telecommunications policy</t>
+        </is>
+      </c>
+      <c r="B2403" t="n">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>office of the administrator. salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2404" t="n">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>office of the comptroller, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2405" t="n">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>office of the director, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2406" t="n">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>office of the general counsel, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2407" t="n">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>office of the secretary, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2408" t="n">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>office or the secretary</t>
+        </is>
+      </c>
+      <c r="B2409" t="n">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>overseas private investment corporation</t>
+        </is>
+      </c>
+      <c r="B2410" t="n">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>pacific ocean area</t>
+        </is>
+      </c>
+      <c r="B2411" t="n">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>parkway and road construction (liquidation of contract authority)</t>
+        </is>
+      </c>
+      <c r="B2412" t="n">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>patient care and special health services</t>
+        </is>
+      </c>
+      <c r="B2413" t="n">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>payment for military service credits</t>
+        </is>
+      </c>
+      <c r="B2414" t="n">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>payment for special benefits for the aged</t>
+        </is>
+      </c>
+      <c r="B2415" t="n">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>payment of sales insufficiencies and interest losses</t>
+        </is>
+      </c>
+      <c r="B2416" t="n">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>payment to the corporation for public broadcasting</t>
+        </is>
+      </c>
+      <c r="B2417" t="n">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>payment to trust funds for health insurance for the aged</t>
+        </is>
+      </c>
+      <c r="B2418" t="n">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>president’s committee on consumer interests</t>
+        </is>
+      </c>
+      <c r="B2419" t="n">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>president’s committee on consumer interests salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2420" t="n">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>president’s council on youth opportunity</t>
+        </is>
+      </c>
+      <c r="B2421" t="n">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>programs for the aging</t>
+        </is>
+      </c>
+      <c r="B2422" t="n">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>public lands development roads and trails
+ (liquidation of contract authority)</t>
+        </is>
+      </c>
+      <c r="B2423" t="n">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>range imrpovements</t>
+        </is>
+      </c>
+      <c r="B2424" t="n">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>recreation</t>
+        </is>
+      </c>
+      <c r="B2425" t="n">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>regional medical programs</t>
+        </is>
+      </c>
+      <c r="B2426" t="n">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>rehabilitation research and training</t>
+        </is>
+      </c>
+      <c r="B2427" t="n">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>rehabilitation services and facilities</t>
+        </is>
+      </c>
+      <c r="B2428" t="n">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>related agencies
+ department of agriculture
+forest service</t>
+        </is>
+      </c>
+      <c r="B2429" t="n">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>related agencies
+ department of health, education, and welfare</t>
+        </is>
+      </c>
+      <c r="B2430" t="n">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>related agency</t>
+        </is>
+      </c>
+      <c r="B2431" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>retired military personnel</t>
+        </is>
+      </c>
+      <c r="B2432" t="n">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>retired pat, defense</t>
+        </is>
+      </c>
+      <c r="B2433" t="n">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>road construction (liquidation of contract authority)</t>
+        </is>
+      </c>
+      <c r="B2434" t="n">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>ryukyu islands, army</t>
+        </is>
+      </c>
+      <c r="B2435" t="n">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>ryukyu islands, army, administration</t>
+        </is>
+      </c>
+      <c r="B2436" t="n">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>salaries and expenses, federal housing administration</t>
+        </is>
+      </c>
+      <c r="B2437" t="n">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>salaries and expenses, metropolitan development</t>
+        </is>
+      </c>
+      <c r="B2438" t="n">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>salaries and expenses, model cities and governmental relations</t>
+        </is>
+      </c>
+      <c r="B2439" t="n">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>salaries and expenses, renewal and housing assistance</t>
+        </is>
+      </c>
+      <c r="B2440" t="n">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>salaries and expenses, united states magistrates</t>
+        </is>
+      </c>
+      <c r="B2441" t="n">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>salaries and expenses, woodrow wilson international center for scholars</t>
+        </is>
+      </c>
+      <c r="B2442" t="n">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>seventeenth naval district</t>
+        </is>
+      </c>
+      <c r="B2443" t="n">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>sixth naval district</t>
+        </is>
+      </c>
+      <c r="B2444" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>social and rehabilitation activities overseas (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2445" t="n">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>social development assistance</t>
+        </is>
+      </c>
+      <c r="B2446" t="n">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>student loan insurance fund</t>
+        </is>
+      </c>
+      <c r="B2447" t="n">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>teachers corps</t>
+        </is>
+      </c>
+      <c r="B2448" t="n">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>tenth naval district</t>
+        </is>
+      </c>
+      <c r="B2449" t="n">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>third naval district</t>
+        </is>
+      </c>
+      <c r="B2450" t="n">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>thirteenth naval district</t>
+        </is>
+      </c>
+      <c r="B2451" t="n">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>twelfth naval district</t>
+        </is>
+      </c>
+      <c r="B2452" t="n">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>u.s soldiers’ home</t>
+        </is>
+      </c>
+      <c r="B2453" t="n">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>unemployment compensation for federal employees and ex-servicemen and trade adjustment activities</t>
+        </is>
+      </c>
+      <c r="B2454" t="n">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>united states army security agency</t>
+        </is>
+      </c>
+      <c r="B2455" t="n">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>united states army strategic communications command</t>
+        </is>
+      </c>
+      <c r="B2456" t="n">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>united states army, europe</t>
+        </is>
+      </c>
+      <c r="B2457" t="n">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>united states army, hawaii</t>
+        </is>
+      </c>
+      <c r="B2458" t="n">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>united states army, pacific</t>
+        </is>
+      </c>
+      <c r="B2459" t="n">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>united states continental army command</t>
+        </is>
+      </c>
+      <c r="B2460" t="n">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>veterans ai ministration</t>
+        </is>
+      </c>
+      <c r="B2461" t="n">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>vocational education</t>
+        </is>
+      </c>
+      <c r="B2462" t="n">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>wage and hour division, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2463" t="n">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>wage and labor standards administration, salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2464" t="n">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>work incentives</t>
+        </is>
+      </c>
+      <c r="B2465" t="n">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>(out of the postal fund)</t>
+        </is>
+      </c>
+      <c r="B2466" t="n">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>aviation advisory commission</t>
+        </is>
+      </c>
+      <c r="B2467" t="n">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>cemeterial expenses, army</t>
+        </is>
+      </c>
+      <c r="B2468" t="n">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>civil supersonic aircraft development termination</t>
+        </is>
+      </c>
+      <c r="B2469" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>commission on american shipbuilding salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2470" t="n">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>commission on marihuana and drug abuse</t>
+        </is>
+      </c>
+      <c r="B2471" t="n">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>commission on the organization of the government of the district of columbia</t>
+        </is>
+      </c>
+      <c r="B2472" t="n">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>corps of engineers civil</t>
+        </is>
+      </c>
+      <c r="B2473" t="n">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>dairy and beekeeper indemnity programs</t>
+        </is>
+      </c>
+      <c r="B2474" t="n">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>darien gap highway</t>
+        </is>
+      </c>
+      <c r="B2475" t="n">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>domestic business activities</t>
+        </is>
+      </c>
+      <c r="B2476" t="n">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>federal labor relations council</t>
+        </is>
+      </c>
+      <c r="B2477" t="n">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>federal-aid highways (trust fund) (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2478" t="n">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>flood control, mississippi river, and tributaries</t>
+        </is>
+      </c>
+      <c r="B2479" t="n">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>foreign direct investment regulation</t>
+        </is>
+      </c>
+      <c r="B2480" t="n">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>highway beautification</t>
+        </is>
+      </c>
+      <c r="B2481" t="n">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>historical and memorial commissions: american revolution bicentennial commission</t>
+        </is>
+      </c>
+      <c r="B2482" t="n">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>homeowners assistance fund, defense</t>
+        </is>
+      </c>
+      <c r="B2483" t="n">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>housing for the elderly or handicapped</t>
+        </is>
+      </c>
+      <c r="B2484" t="n">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>independent agencies</t>
+        </is>
+      </c>
+      <c r="B2485" t="n">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>international commissions
+ international boundary and water commission, united states and mexico:</t>
+        </is>
+      </c>
+      <c r="B2486" t="n">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>leadership automobiles</t>
+        </is>
+      </c>
+      <c r="B2487" t="n">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>national commission on fire prevention and control</t>
+        </is>
+      </c>
+      <c r="B2488" t="n">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>national commission on materials policy</t>
+        </is>
+      </c>
+      <c r="B2489" t="n">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>national industrial pollution control council</t>
+        </is>
+      </c>
+      <c r="B2490" t="n">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>national tourism resources review commission</t>
+        </is>
+      </c>
+      <c r="B2491" t="n">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>office of management and budget</t>
+        </is>
+      </c>
+      <c r="B2492" t="n">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>office of telecommunications</t>
+        </is>
+      </c>
+      <c r="B2493" t="n">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>operations, research, and facilities</t>
+        </is>
+      </c>
+      <c r="B2494" t="n">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>other weapons</t>
+        </is>
+      </c>
+      <c r="B2495" t="n">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>president’s advisory council on executive organization</t>
+        </is>
+      </c>
+      <c r="B2496" t="n">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>public facility’ loans</t>
+        </is>
+      </c>
+      <c r="B2497" t="n">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>research, development, test, and evaluation</t>
+        </is>
+      </c>
+      <c r="B2498" t="n">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>revolving fund (liquidating programs)</t>
+        </is>
+      </c>
+      <c r="B2499" t="n">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>salaries and expenses, revision of annotated constitution</t>
+        </is>
+      </c>
+      <c r="B2500" t="n">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>salaries and expenses, revision of hinds’ and cannon’s precedents</t>
+        </is>
+      </c>
+      <c r="B2501" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>torpedoes</t>
+        </is>
+      </c>
+      <c r="B2502" t="n">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>tracked combat vehicles</t>
+        </is>
+      </c>
+      <c r="B2503" t="n">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>u.s. soldiers’ home</t>
+        </is>
+      </c>
+      <c r="B2504" t="n">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>underground electric power transmission research</t>
+        </is>
+      </c>
+      <c r="B2505" t="n">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>united states tax court</t>
+        </is>
+      </c>
+      <c r="B2506" t="n">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>1872 economic censuses</t>
+        </is>
+      </c>
+      <c r="B2507" t="n">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>1974 census of agriculture</t>
+        </is>
+      </c>
+      <c r="B2508" t="n">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>accounts, collection and taxpayer service</t>
+        </is>
+      </c>
+      <c r="B2509" t="n">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>annexed budgets</t>
+        </is>
+      </c>
+      <c r="B2510" t="n">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>books for the blind and physically handicapped</t>
+        </is>
+      </c>
+      <c r="B2511" t="n">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>bureau of alcohol, tobacco and firearms</t>
+        </is>
+      </c>
+      <c r="B2512" t="n">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>bureau of engraving and printing fund</t>
+        </is>
+      </c>
+      <c r="B2513" t="n">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>bureau of prisons</t>
+        </is>
+      </c>
+      <c r="B2514" t="n">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>bureau or indian affairs</t>
+        </is>
+      </c>
+      <c r="B2515" t="n">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>capitol guide service</t>
+        </is>
+      </c>
+      <c r="B2516" t="n">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>claims and treaty obligations
+ alaska native fund</t>
+        </is>
+      </c>
+      <c r="B2517" t="n">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>collection and distribution of library materials (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2518" t="n">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>commission on american shipbuilding</t>
+        </is>
+      </c>
+      <c r="B2519" t="n">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>commission on bankruptcy law’s of the united states</t>
+        </is>
+      </c>
+      <c r="B2520" t="n">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>commission on executive, legislative, and judicial salaries</t>
+        </is>
+      </c>
+      <c r="B2521" t="n">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>commission on international radio broadcasting</t>
+        </is>
+      </c>
+      <c r="B2522" t="n">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>commission on railroad retirement</t>
+        </is>
+      </c>
+      <c r="B2523" t="n">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>committee for purchase of products and services of the blind and other severely handicapped</t>
+        </is>
+      </c>
+      <c r="B2524" t="n">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>committee for the purchase of products and services of the blind and other severely handicapped</t>
+        </is>
+      </c>
+      <c r="B2525" t="n">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>community development</t>
+        </is>
+      </c>
+      <c r="B2526" t="n">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>community planning and management</t>
+        </is>
+      </c>
+      <c r="B2527" t="n">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>compensation and mileage of the vice president and senators</t>
+        </is>
+      </c>
+      <c r="B2528" t="n">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>compensation and mileage of the vice president and senators and expense allowances of the vice president and leaders of the senate</t>
+        </is>
+      </c>
+      <c r="B2529" t="n">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>compilation of precedents of house of representatives</t>
+        </is>
+      </c>
+      <c r="B2530" t="n">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>congressional research service</t>
+        </is>
+      </c>
+      <c r="B2531" t="n">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>construction and land acquisition</t>
+        </is>
+      </c>
+      <c r="B2532" t="n">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>consumer protective marketing and regulatory programs</t>
+        </is>
+      </c>
+      <c r="B2533" t="n">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>cost-accounting standards board</t>
+        </is>
+      </c>
+      <c r="B2534" t="n">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>council, of economic advisers</t>
+        </is>
+      </c>
+      <c r="B2535" t="n">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>department of defense
+ civil defense preparedness agency</t>
+        </is>
+      </c>
+      <c r="B2536" t="n">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>director of test and evaluation, defense</t>
+        </is>
+      </c>
+      <c r="B2537" t="n">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>disaster loan fund</t>
+        </is>
+      </c>
+      <c r="B2538" t="n">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>disaster loan fund
+ business loan and investment fund
+lease and surety bond guarantees revolving fund</t>
+        </is>
+      </c>
+      <c r="B2539" t="n">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>domestic council</t>
+        </is>
+      </c>
+      <c r="B2540" t="n">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>economic stabilization activities</t>
+        </is>
+      </c>
+      <c r="B2541" t="n">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>environmental services</t>
+        </is>
+      </c>
+      <c r="B2542" t="n">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>executive residence</t>
+        </is>
+      </c>
+      <c r="B2543" t="n">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>expense allowances of the vice president and majority and minority leaders</t>
+        </is>
+      </c>
+      <c r="B2544" t="n">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>export-import bank op the united states</t>
+        </is>
+      </c>
+      <c r="B2545" t="n">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>federal payment to the airport and airway trust fund</t>
+        </is>
+      </c>
+      <c r="B2546" t="n">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>federal savings and loan insurance corporation</t>
+        </is>
+      </c>
+      <c r="B2547" t="n">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>federal supply service</t>
+        </is>
+      </c>
+      <c r="B2548" t="n">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>federal workmen’s compensation benefits</t>
+        </is>
+      </c>
+      <c r="B2549" t="n">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>federal, prison system</t>
+        </is>
+      </c>
+      <c r="B2550" t="n">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>financial and technical assistance</t>
+        </is>
+      </c>
+      <c r="B2551" t="n">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>foreign assistance</t>
+        </is>
+      </c>
+      <c r="B2552" t="n">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>general services administration
+ public buildings service</t>
+        </is>
+      </c>
+      <c r="B2553" t="n">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>government contributions</t>
+        </is>
+      </c>
+      <c r="B2554" t="n">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>grants to national railroad passenger corporation</t>
+        </is>
+      </c>
+      <c r="B2555" t="n">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>historical and memorial commission</t>
+        </is>
+      </c>
+      <c r="B2556" t="n">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>housing management</t>
+        </is>
+      </c>
+      <c r="B2557" t="n">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>housing production and mortgage credit</t>
+        </is>
+      </c>
+      <c r="B2558" t="n">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>intergovernmental personnel assistance</t>
+        </is>
+      </c>
+      <c r="B2559" t="n">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>international radio broadcasting activities</t>
+        </is>
+      </c>
+      <c r="B2560" t="n">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>joint committee on congressional operations</t>
+        </is>
+      </c>
+      <c r="B2561" t="n">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>joint committee on inaugural ceremonies of 1973</t>
+        </is>
+      </c>
+      <c r="B2562" t="n">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>joint committee on reduction of federal expenditures</t>
+        </is>
+      </c>
+      <c r="B2563" t="n">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>joint federal-state land use planning commission for alaska</t>
+        </is>
+      </c>
+      <c r="B2564" t="n">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>limitation on grants to states for unemployment insurance and employment services</t>
+        </is>
+      </c>
+      <c r="B2565" t="n">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>manpower training services</t>
+        </is>
+      </c>
+      <c r="B2566" t="n">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>medical facilities guarantee and loan fund</t>
+        </is>
+      </c>
+      <c r="B2567" t="n">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>micronesian claims fund</t>
+        </is>
+      </c>
+      <c r="B2568" t="n">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>national archives and records service</t>
+        </is>
+      </c>
+      <c r="B2569" t="n">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>national commission on productivity</t>
+        </is>
+      </c>
+      <c r="B2570" t="n">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>national highway traffic safety administration</t>
+        </is>
+      </c>
+      <c r="B2571" t="n">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>new edition of the district of columbia code</t>
+        </is>
+      </c>
+      <c r="B2572" t="n">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>office of intergovernmental relations</t>
+        </is>
+      </c>
+      <c r="B2573" t="n">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>office of the attending physician</t>
+        </is>
+      </c>
+      <c r="B2574" t="n">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>office of the president pro tempore</t>
+        </is>
+      </c>
+      <c r="B2575" t="n">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>offices of the majority and minority leaders</t>
+        </is>
+      </c>
+      <c r="B2576" t="n">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>offices of the secretaries for the majority and minority</t>
+        </is>
+      </c>
+      <c r="B2577" t="n">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>official mail costs</t>
+        </is>
+      </c>
+      <c r="B2578" t="n">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>operation and maintenance. navy</t>
+        </is>
+      </c>
+      <c r="B2579" t="n">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>payment of government losses in shipment</t>
+        </is>
+      </c>
+      <c r="B2580" t="n">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>payment to the postal. service fund</t>
+        </is>
+      </c>
+      <c r="B2581" t="n">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>payments to widows and heirs of deceased members of congress</t>
+        </is>
+      </c>
+      <c r="B2582" t="n">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>postage stamp allowances</t>
+        </is>
+      </c>
+      <c r="B2583" t="n">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>procurement, marine cores</t>
+        </is>
+      </c>
+      <c r="B2584" t="n">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>property management and disposal service</t>
+        </is>
+      </c>
+      <c r="B2585" t="n">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>public buildings service</t>
+        </is>
+      </c>
+      <c r="B2586" t="n">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>records declassification</t>
+        </is>
+      </c>
+      <c r="B2587" t="n">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>regional action planning commissions</t>
+        </is>
+      </c>
+      <c r="B2588" t="n">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>regional development programs</t>
+        </is>
+      </c>
+      <c r="B2589" t="n">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>related agencies
+ department of agriculture</t>
+        </is>
+      </c>
+      <c r="B2590" t="n">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>representation by court-appointed counsel and operation of defender organizations</t>
+        </is>
+      </c>
+      <c r="B2591" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>research, development and facilities</t>
+        </is>
+      </c>
+      <c r="B2592" t="n">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>research, engineering, analysis, and technical services</t>
+        </is>
+      </c>
+      <c r="B2593" t="n">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>research, shelter survey, and marking</t>
+        </is>
+      </c>
+      <c r="B2594" t="n">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>revision of hinds’ and cannon’s precedents</t>
+        </is>
+      </c>
+      <c r="B2595" t="n">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>salaries and expenses of united states magistrates</t>
+        </is>
+      </c>
+      <c r="B2596" t="n">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>science information exchange</t>
+        </is>
+      </c>
+      <c r="B2597" t="n">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>security supporting assistance</t>
+        </is>
+      </c>
+      <c r="B2598" t="n">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>senate garage</t>
+        </is>
+      </c>
+      <c r="B2599" t="n">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>social and economic statistics administration</t>
+        </is>
+      </c>
+      <c r="B2600" t="n">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>soldiers’ home</t>
+        </is>
+      </c>
+      <c r="B2601" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>special action office for drug abuse prevention</t>
+        </is>
+      </c>
+      <c r="B2602" t="n">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>special assistance to the president</t>
+        </is>
+      </c>
+      <c r="B2603" t="n">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>special international exhibitions (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2604" t="n">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>state boating safety assistance</t>
+        </is>
+      </c>
+      <c r="B2605" t="n">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>temporary study commissions</t>
+        </is>
+      </c>
+      <c r="B2606" t="n">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>transportation and communications services</t>
+        </is>
+      </c>
+      <c r="B2607" t="n">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>abatement and control</t>
+        </is>
+      </c>
+      <c r="B2608" t="n">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>acquisition of lands fob national forests</t>
+        </is>
+      </c>
+      <c r="B2609" t="n">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>acquisition of site</t>
+        </is>
+      </c>
+      <c r="B2610" t="n">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>acquisition. construction, and improvements</t>
+        </is>
+      </c>
+      <c r="B2611" t="n">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>additional parking facilities for congressional employees</t>
+        </is>
+      </c>
+      <c r="B2612" t="n">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>administration and staff services</t>
+        </is>
+      </c>
+      <c r="B2613" t="n">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>administration of economic development assistance programs</t>
+        </is>
+      </c>
+      <c r="B2614" t="n">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>administrative and other expenses, state</t>
+        </is>
+      </c>
+      <c r="B2615" t="n">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>advances to the environmental financing authority fund</t>
+        </is>
+      </c>
+      <c r="B2616" t="n">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>advisory committee on federal pay</t>
+        </is>
+      </c>
+      <c r="B2617" t="n">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="2618">
+      <c r="A2618" t="inlineStr">
+        <is>
+          <t>agency and regional management</t>
+        </is>
+      </c>
+      <c r="B2618" t="n">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>agency contributions and longevity compensation</t>
+        </is>
+      </c>
+      <c r="B2619" t="n">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" t="inlineStr">
+        <is>
+          <t>agricultural conservation program (reap)</t>
+        </is>
+      </c>
+      <c r="B2620" t="n">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>agricultural credit insurance fund</t>
+        </is>
+      </c>
+      <c r="B2621" t="n">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="2622">
+      <c r="A2622" t="inlineStr">
+        <is>
+          <t>agricultural economics</t>
+        </is>
+      </c>
+      <c r="B2622" t="n">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>aims control and disarmament agency</t>
+        </is>
+      </c>
+      <c r="B2623" t="n">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>alaska native fund</t>
+        </is>
+      </c>
+      <c r="B2624" t="n">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>allowances and office staff for former president</t>
+        </is>
+      </c>
+      <c r="B2625" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>alteration of bridges</t>
+        </is>
+      </c>
+      <c r="B2626" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>american-revolution bicentennial commission</t>
+        </is>
+      </c>
+      <c r="B2627" t="n">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>animal and plant health inspection service</t>
+        </is>
+      </c>
+      <c r="B2628" t="n">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>assistance for health manpower training institutions</t>
+        </is>
+      </c>
+      <c r="B2629" t="n">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>assistance to refugees from the soviet union</t>
+        </is>
+      </c>
+      <c r="B2630" t="n">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>automated data and telecommunications service</t>
+        </is>
+      </c>
+      <c r="B2631" t="n">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="inlineStr">
+        <is>
+          <t>bureau or labor statistics</t>
+        </is>
+      </c>
+      <c r="B2632" t="n">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>capitalization of rural telephone bank</t>
+        </is>
+      </c>
+      <c r="B2633" t="n">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" t="inlineStr">
+        <is>
+          <t>child development</t>
+        </is>
+      </c>
+      <c r="B2634" t="n">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="2635">
+      <c r="A2635" t="inlineStr">
+        <is>
+          <t>coastal zone management</t>
+        </is>
+      </c>
+      <c r="B2635" t="n">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="2636">
+      <c r="A2636" t="inlineStr">
+        <is>
+          <t>commission of the review of national policy toward gambling</t>
+        </is>
+      </c>
+      <c r="B2636" t="n">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="inlineStr">
+        <is>
+          <t>commission on civil eights</t>
+        </is>
+      </c>
+      <c r="B2637" t="n">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" t="inlineStr">
+        <is>
+          <t>commission on highway beautification</t>
+        </is>
+      </c>
+      <c r="B2638" t="n">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="inlineStr">
+        <is>
+          <t>commission on revision of the federal court appellate system of the united states</t>
+        </is>
+      </c>
+      <c r="B2639" t="n">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" t="inlineStr">
+        <is>
+          <t>commission on the organization or the government for the conduct of foreign policy</t>
+        </is>
+      </c>
+      <c r="B2640" t="n">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" t="inlineStr">
+        <is>
+          <t>commodity programs</t>
+        </is>
+      </c>
+      <c r="B2641" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" t="inlineStr">
+        <is>
+          <t>construction
+ (appropriation to liquidate contract authority)</t>
+        </is>
+      </c>
+      <c r="B2642" t="n">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" t="inlineStr">
+        <is>
+          <t>construction and anadromous fish</t>
+        </is>
+      </c>
+      <c r="B2643" t="n">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" t="inlineStr">
+        <is>
+          <t>construction and operation of recreation facilities</t>
+        </is>
+      </c>
+      <c r="B2644" t="n">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" t="inlineStr">
+        <is>
+          <t>consumer programs</t>
+        </is>
+      </c>
+      <c r="B2645" t="n">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" t="inlineStr">
+        <is>
+          <t>contribution to interstate commission on the potomac river babin</t>
+        </is>
+      </c>
+      <c r="B2646" t="n">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" t="inlineStr">
+        <is>
+          <t>courts of appeals, district courts, and other judical services</t>
+        </is>
+      </c>
+      <c r="B2647" t="n">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" t="inlineStr">
+        <is>
+          <t>defense manpower commission</t>
+        </is>
+      </c>
+      <c r="B2648" t="n">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="inlineStr">
+        <is>
+          <t>department of agriculture
+ departmental management</t>
+        </is>
+      </c>
+      <c r="B2649" t="n">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" t="inlineStr">
+        <is>
+          <t>department of agriculture
+ food and nutrition service</t>
+        </is>
+      </c>
+      <c r="B2650" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="inlineStr">
+        <is>
+          <t>department of agriculture
+ soil conservation service</t>
+        </is>
+      </c>
+      <c r="B2651" t="n">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" t="inlineStr">
+        <is>
+          <t>department of defense
+ defense civil preparedness agency</t>
+        </is>
+      </c>
+      <c r="B2652" t="n">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="inlineStr">
+        <is>
+          <t>department of the treasury
+ bureau of accounts</t>
+        </is>
+      </c>
+      <c r="B2653" t="n">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="inlineStr">
+        <is>
+          <t>department or health, education, and welfare</t>
+        </is>
+      </c>
+      <c r="B2654" t="n">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="inlineStr">
+        <is>
+          <t>department or transportation</t>
+        </is>
+      </c>
+      <c r="B2655" t="n">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="inlineStr">
+        <is>
+          <t>departmental management
+ salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2656" t="n">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="inlineStr">
+        <is>
+          <t>departmental operations</t>
+        </is>
+      </c>
+      <c r="B2657" t="n">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" t="inlineStr">
+        <is>
+          <t>disaster loan fund
+ business loan and investment fund</t>
+        </is>
+      </c>
+      <c r="B2658" t="n">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>disaster relief assistance</t>
+        </is>
+      </c>
+      <c r="B2659" t="n">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="inlineStr">
+        <is>
+          <t>domestic and international business administration</t>
+        </is>
+      </c>
+      <c r="B2660" t="n">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="inlineStr">
+        <is>
+          <t>education division</t>
+        </is>
+      </c>
+      <c r="B2661" t="n">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" t="inlineStr">
+        <is>
+          <t>educational activities overseas (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2662" t="n">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>educational development</t>
+        </is>
+      </c>
+      <c r="B2663" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="inlineStr">
+        <is>
+          <t>emergency military assistance for cambodia</t>
+        </is>
+      </c>
+      <c r="B2664" t="n">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>emergency preparedness
+ salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2665" t="n">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="inlineStr">
+        <is>
+          <t>emergency rail facilities restoration</t>
+        </is>
+      </c>
+      <c r="B2666" t="n">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>emergency school assistance</t>
+        </is>
+      </c>
+      <c r="B2667" t="n">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="inlineStr">
+        <is>
+          <t>emergency security assistance for israel</t>
+        </is>
+      </c>
+      <c r="B2668" t="n">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>enforcement</t>
+        </is>
+      </c>
+      <c r="B2669" t="n">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="inlineStr">
+        <is>
+          <t>engineering and development</t>
+        </is>
+      </c>
+      <c r="B2670" t="n">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>environmental financing authority fund</t>
+        </is>
+      </c>
+      <c r="B2671" t="n">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="inlineStr">
+        <is>
+          <t>environmental programs</t>
+        </is>
+      </c>
+      <c r="B2672" t="n">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>facilities and equipment (airport and airway trust fund)</t>
+        </is>
+      </c>
+      <c r="B2673" t="n">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" t="inlineStr">
+        <is>
+          <t>federal grants to states for employment services</t>
+        </is>
+      </c>
+      <c r="B2674" t="n">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="2675">
+      <c r="A2675" t="inlineStr">
+        <is>
+          <t>federal labor relations council
+ salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B2675" t="n">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2676">
+      <c r="A2676" t="inlineStr">
+        <is>
+          <t>federal-aid highways (liquidation of contract authorization) (trust fund)</t>
+        </is>
+      </c>
+      <c r="B2676" t="n">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>fish and wildlife and parks</t>
+        </is>
+      </c>
+      <c r="B2677" t="n">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" t="inlineStr">
+        <is>
+          <t>fisherman’s guaranty fund</t>
+        </is>
+      </c>
+      <c r="B2678" t="n">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>foreign operations</t>
+        </is>
+      </c>
+      <c r="B2679" t="n">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" t="inlineStr">
+        <is>
+          <t>forest highways (liquidation of (contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2680" t="n">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" t="inlineStr">
+        <is>
+          <t>funds appropriated to the president
+ international financial institutions</t>
+        </is>
+      </c>
+      <c r="B2681" t="n">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" t="inlineStr">
+        <is>
+          <t>funds for strengthening markets, income, and supply (section 32)</t>
+        </is>
+      </c>
+      <c r="B2682" t="n">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>general provisions—general services administration</t>
+        </is>
+      </c>
+      <c r="B2683" t="n">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" t="inlineStr">
+        <is>
+          <t>general provisions—treasury department</t>
+        </is>
+      </c>
+      <c r="B2684" t="n">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>grants to the national railroad passenger corporation</t>
+        </is>
+      </c>
+      <c r="B2685" t="n">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" t="inlineStr">
+        <is>
+          <t>grants-in-aid fob railroad safety</t>
+        </is>
+      </c>
+      <c r="B2686" t="n">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>grants-in-aid for airports (airport and airway trust fund)</t>
+        </is>
+      </c>
+      <c r="B2687" t="n">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" t="inlineStr">
+        <is>
+          <t>grants-in-aid for natural gas pipeline safety</t>
+        </is>
+      </c>
+      <c r="B2688" t="n">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>health professions education fund</t>
+        </is>
+      </c>
+      <c r="B2689" t="n">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>health services delivery</t>
+        </is>
+      </c>
+      <c r="B2690" t="n">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>health services planning and development</t>
+        </is>
+      </c>
+      <c r="B2691" t="n">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" t="inlineStr">
+        <is>
+          <t>higher education facilities loan and insurance fund</t>
+        </is>
+      </c>
+      <c r="B2692" t="n">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>highway-related safety grants (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2693" t="n">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" t="inlineStr">
+        <is>
+          <t>housing payments</t>
+        </is>
+      </c>
+      <c r="B2694" t="n">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>independent agencies
+ farm credit administration</t>
+        </is>
+      </c>
+      <c r="B2695" t="n">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" t="inlineStr">
+        <is>
+          <t>independent agency
+ action—international programs</t>
+        </is>
+      </c>
+      <c r="B2696" t="n">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>indian education</t>
+        </is>
+      </c>
+      <c r="B2697" t="n">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" t="inlineStr">
+        <is>
+          <t>indian tribal claims</t>
+        </is>
+      </c>
+      <c r="B2698" t="n">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>indochina postwar reconstruction assistance</t>
+        </is>
+      </c>
+      <c r="B2699" t="n">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" t="inlineStr">
+        <is>
+          <t>inter-american foundation</t>
+        </is>
+      </c>
+      <c r="B2700" t="n">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>interest subsidy</t>
+        </is>
+      </c>
+      <c r="B2701" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" t="inlineStr">
+        <is>
+          <t>international programs</t>
+        </is>
+      </c>
+      <c r="B2702" t="n">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>international radio broadcasting</t>
+        </is>
+      </c>
+      <c r="B2703" t="n">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" t="inlineStr">
+        <is>
+          <t>international trade negotiations</t>
+        </is>
+      </c>
+      <c r="B2704" t="n">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>investment in asian development bank</t>
+        </is>
+      </c>
+      <c r="B2705" t="n">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" t="inlineStr">
+        <is>
+          <t>investment in international development association</t>
+        </is>
+      </c>
+      <c r="B2706" t="n">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>joint committee on inaugural ceremonies, 1973</t>
+        </is>
+      </c>
+      <c r="B2707" t="n">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" t="inlineStr">
+        <is>
+          <t>library resources</t>
+        </is>
+      </c>
+      <c r="B2708" t="n">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>limitation on administrative and vocational  training expenses, federal prison industries, incorporated</t>
+        </is>
+      </c>
+      <c r="B2709" t="n">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="inlineStr">
+        <is>
+          <t>liquidation op contract authorization</t>
+        </is>
+      </c>
+      <c r="B2710" t="n">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>mines and minerals</t>
+        </is>
+      </c>
+      <c r="B2711" t="n">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="inlineStr">
+        <is>
+          <t>modifications and enlargement, capitol power plant</t>
+        </is>
+      </c>
+      <c r="B2712" t="n">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>national commission for the review of federal and state laws relating to wiretapping and electronic surveillance</t>
+        </is>
+      </c>
+      <c r="B2713" t="n">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>national commission on water quality</t>
+        </is>
+      </c>
+      <c r="B2714" t="n">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>national institute of arthritis, metabolism, and digestive diseases</t>
+        </is>
+      </c>
+      <c r="B2715" t="n">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>national institute of education</t>
+        </is>
+      </c>
+      <c r="B2716" t="n">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>new edition of the united states code</t>
+        </is>
+      </c>
+      <c r="B2717" t="n">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>nutrition program for the elderly</t>
+        </is>
+      </c>
+      <c r="B2718" t="n">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>occupational, vocational, and adult education</t>
+        </is>
+      </c>
+      <c r="B2719" t="n">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>office of superintendent’ of documents</t>
+        </is>
+      </c>
+      <c r="B2720" t="n">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>office of technology assessment</t>
+        </is>
+      </c>
+      <c r="B2721" t="n">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>office of the assistant secretary for education</t>
+        </is>
+      </c>
+      <c r="B2722" t="n">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>operating expenses, domestic programs</t>
+        </is>
+      </c>
+      <c r="B2723" t="n">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>participation in united states expositions</t>
+        </is>
+      </c>
+      <c r="B2724" t="n">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>payment of sales insufficiences and interest losses</t>
+        </is>
+      </c>
+      <c r="B2725" t="n">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>payment of vietnam and u.s.s. pueblo prisoner of war claims</t>
+        </is>
+      </c>
+      <c r="B2726" t="n">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>payment to international center
+ washington, district of columbia</t>
+        </is>
+      </c>
+      <c r="B2727" t="n">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>payment to the postal service fund</t>
+        </is>
+      </c>
+      <c r="B2728" t="n">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>payments for military service credits</t>
+        </is>
+      </c>
+      <c r="B2729" t="n">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>pennsylvania avenue development corporation</t>
+        </is>
+      </c>
+      <c r="B2730" t="n">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>personal services</t>
+        </is>
+      </c>
+      <c r="B2731" t="n">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>pharmacological research</t>
+        </is>
+      </c>
+      <c r="B2732" t="n">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>planning and construction</t>
+        </is>
+      </c>
+      <c r="B2733" t="n">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>planning, development and operation of recreation facilities</t>
+        </is>
+      </c>
+      <c r="B2734" t="n">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>post secondary innovation</t>
+        </is>
+      </c>
+      <c r="B2735" t="n">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>preventive health services</t>
+        </is>
+      </c>
+      <c r="B2736" t="n">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>procurement or ammunition, army</t>
+        </is>
+      </c>
+      <c r="B2737" t="n">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>procurement or weapons and tracked combat vehicles, army</t>
+        </is>
+      </c>
+      <c r="B2738" t="n">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>rail crossings—demonstration projects</t>
+        </is>
+      </c>
+      <c r="B2739" t="n">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>railroad safety</t>
+        </is>
+      </c>
+      <c r="B2740" t="n">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>railroad-highway crossings demonstration projects</t>
+        </is>
+      </c>
+      <c r="B2741" t="n">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>recreation development and operation of recreation facilities</t>
+        </is>
+      </c>
+      <c r="B2742" t="n">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>representation by court-appointed council and operation of defender organizations</t>
+        </is>
+      </c>
+      <c r="B2743" t="n">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>research, development, and demonstrations and university research and training</t>
+        </is>
+      </c>
+      <c r="B2744" t="n">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>research, engineering and development (airport and airway trust fund)</t>
+        </is>
+      </c>
+      <c r="B2745" t="n">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>rural development grants and technical assistance</t>
+        </is>
+      </c>
+      <c r="B2746" t="n">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>rural development insurance fund</t>
+        </is>
+      </c>
+      <c r="B2747" t="n">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>rural development service</t>
+        </is>
+      </c>
+      <c r="B2748" t="n">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>rural electrification and telephone revolving fund loan authorizations</t>
+        </is>
+      </c>
+      <c r="B2749" t="n">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>rural telephone bank</t>
+        </is>
+      </c>
+      <c r="B2750" t="n">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>salaries and expenses, assistant secretary for education</t>
+        </is>
+      </c>
+      <c r="B2751" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>salaries and expenses, community development programs</t>
+        </is>
+      </c>
+      <c r="B2752" t="n">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>salaries and expenses, community planning and management programs</t>
+        </is>
+      </c>
+      <c r="B2753" t="n">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>salaries and expenses, housing management programs</t>
+        </is>
+      </c>
+      <c r="B2754" t="n">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>salaries and expenses, housing production and mortgage credit programs</t>
+        </is>
+      </c>
+      <c r="B2755" t="n">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>salaries and expenses, office of general counsel</t>
+        </is>
+      </c>
+      <c r="B2756" t="n">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>salaries and expenses, office of inspector general</t>
+        </is>
+      </c>
+      <c r="B2757" t="n">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>science and education programs</t>
+        </is>
+      </c>
+      <c r="B2758" t="n">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>science and technology</t>
+        </is>
+      </c>
+      <c r="B2759" t="n">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>scientific activities overseas
+ (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2760" t="n">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>social and rehabilitation services</t>
+        </is>
+      </c>
+      <c r="B2761" t="n">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>special fund for drug abuse</t>
+        </is>
+      </c>
+      <c r="B2762" t="n">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>special payments to international financial institutions</t>
+        </is>
+      </c>
+      <c r="B2763" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>special recreation use fees</t>
+        </is>
+      </c>
+      <c r="B2764" t="n">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>territorial affairs</t>
+        </is>
+      </c>
+      <c r="B2765" t="n">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>territorial highways (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2766" t="n">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>the alaska railroad</t>
+        </is>
+      </c>
+      <c r="B2767" t="n">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>this act</t>
+        </is>
+      </c>
+      <c r="B2768" t="n">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>united states soldiers’ and airmen’s home</t>
+        </is>
+      </c>
+      <c r="B2769" t="n">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="inlineStr">
+        <is>
+          <t>water bank program</t>
+        </is>
+      </c>
+      <c r="B2770" t="n">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>youth conservation corps</t>
+        </is>
+      </c>
+      <c r="B2771" t="n">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
+          <t>(including rescission)</t>
+        </is>
+      </c>
+      <c r="B2772" t="n">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>(transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2773" t="n">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>access highways to public recreation areas on certain lakes</t>
+        </is>
+      </c>
+      <c r="B2774" t="n">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>administrative and staff support services</t>
+        </is>
+      </c>
+      <c r="B2775" t="n">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>administrative office of the united states courts
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2776" t="n">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>advances to the unemployment trust fund and other funds</t>
+        </is>
+      </c>
+      <c r="B2777" t="n">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>alterations and improvements, buildings and grounds, to provide facilities for the physically handicapped</t>
+        </is>
+      </c>
+      <c r="B2778" t="n">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>american indian policy review commission</t>
+        </is>
+      </c>
+      <c r="B2779" t="n">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>american revolution bicentennial administration</t>
+        </is>
+      </c>
+      <c r="B2780" t="n">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>appalachlin regional commission</t>
+        </is>
+      </c>
+      <c r="B2781" t="n">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>assistance to palestinian refugees</t>
+        </is>
+      </c>
+      <c r="B2782" t="n">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>assistant secretary for human development</t>
+        </is>
+      </c>
+      <c r="B2783" t="n">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>assistant secretary tor health</t>
+        </is>
+      </c>
+      <c r="B2784" t="n">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>bicentennial activities</t>
+        </is>
+      </c>
+      <c r="B2785" t="n">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>bicentennial expenses, the judiciary</t>
+        </is>
+      </c>
+      <c r="B2786" t="n">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>bikeway program</t>
+        </is>
+      </c>
+      <c r="B2787" t="n">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>bureau of alcohol, tobacco, and fire arms</t>
+        </is>
+      </c>
+      <c r="B2788" t="n">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>coast guard supply fund</t>
+        </is>
+      </c>
+      <c r="B2789" t="n">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>colorado river basin salinity control projects</t>
+        </is>
+      </c>
+      <c r="B2790" t="n">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>comers or appeals, district courts, and other judicial services</t>
+        </is>
+      </c>
+      <c r="B2791" t="n">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>commission on federal paperwork</t>
+        </is>
+      </c>
+      <c r="B2792" t="n">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>commission on fine arts</t>
+        </is>
+      </c>
+      <c r="B2793" t="n">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>committee on appropriations (investigations)</t>
+        </is>
+      </c>
+      <c r="B2794" t="n">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>committee on appropriations (studies and investigations)</t>
+        </is>
+      </c>
+      <c r="B2795" t="n">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>committee on the budget (studies)</t>
+        </is>
+      </c>
+      <c r="B2796" t="n">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>commodity futures trading commission</t>
+        </is>
+      </c>
+      <c r="B2797" t="n">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>community development grants and transfer of unexpended balance</t>
+        </is>
+      </c>
+      <c r="B2798" t="n">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>community services administration</t>
+        </is>
+      </c>
+      <c r="B2799" t="n">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>community services program</t>
+        </is>
+      </c>
+      <c r="B2800" t="n">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>compensation and mileage for the members</t>
+        </is>
+      </c>
+      <c r="B2801" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>comprehensive manpower assistance</t>
+        </is>
+      </c>
+      <c r="B2802" t="n">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>conservation</t>
+        </is>
+      </c>
+      <c r="B2803" t="n">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>construction (appropriation to liquidate contract authority)</t>
+        </is>
+      </c>
+      <c r="B2804" t="n">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>construction of an extension to the new senate office building</t>
+        </is>
+      </c>
+      <c r="B2805" t="n">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>department of health, education, and welfare
+ health services administration</t>
+        </is>
+      </c>
+      <c r="B2806" t="n">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>department op the army
+ corps of engineers—civil</t>
+        </is>
+      </c>
+      <c r="B2807" t="n">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>educational, exchange</t>
+        </is>
+      </c>
+      <c r="B2808" t="n">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" t="inlineStr">
+        <is>
+          <t>emergency homeowners’ relief fund</t>
+        </is>
+      </c>
+      <c r="B2809" t="n">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" t="inlineStr">
+        <is>
+          <t>emergency mortgage purchase assistance</t>
+        </is>
+      </c>
+      <c r="B2810" t="n">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" t="inlineStr">
+        <is>
+          <t>emergency school aid</t>
+        </is>
+      </c>
+      <c r="B2811" t="n">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" t="inlineStr">
+        <is>
+          <t>energy and minerals</t>
+        </is>
+      </c>
+      <c r="B2812" t="n">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" t="inlineStr">
+        <is>
+          <t>energy research and development</t>
+        </is>
+      </c>
+      <c r="B2813" t="n">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" t="inlineStr">
+        <is>
+          <t>energy research and development administration</t>
+        </is>
+      </c>
+      <c r="B2814" t="n">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" t="inlineStr">
+        <is>
+          <t>ex gratia payment, bikini atoll</t>
+        </is>
+      </c>
+      <c r="B2815" t="n">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" t="inlineStr">
+        <is>
+          <t>facilities, engineering and development</t>
+        </is>
+      </c>
+      <c r="B2816" t="n">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" t="inlineStr">
+        <is>
+          <t>family housing</t>
+        </is>
+      </c>
+      <c r="B2817" t="n">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" t="inlineStr">
+        <is>
+          <t>farm income stabilization</t>
+        </is>
+      </c>
+      <c r="B2818" t="n">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" t="inlineStr">
+        <is>
+          <t>federal buildings fund</t>
+        </is>
+      </c>
+      <c r="B2819" t="n">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" t="inlineStr">
+        <is>
+          <t>federal election commission</t>
+        </is>
+      </c>
+      <c r="B2820" t="n">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" t="inlineStr">
+        <is>
+          <t>federal energy administration</t>
+        </is>
+      </c>
+      <c r="B2821" t="n">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" t="inlineStr">
+        <is>
+          <t>federal management policy</t>
+        </is>
+      </c>
+      <c r="B2822" t="n">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" t="inlineStr">
+        <is>
+          <t>food donations program</t>
+        </is>
+      </c>
+      <c r="B2823" t="n">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" t="inlineStr">
+        <is>
+          <t>forestry incentives program</t>
+        </is>
+      </c>
+      <c r="B2824" t="n">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" t="inlineStr">
+        <is>
+          <t>furniture and furnishings
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2825" t="n">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" t="inlineStr">
+        <is>
+          <t>grants-in-aid for railroad safety</t>
+        </is>
+      </c>
+      <c r="B2826" t="n">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" t="inlineStr">
+        <is>
+          <t>health resources administration
+ health resources</t>
+        </is>
+      </c>
+      <c r="B2827" t="n">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" t="inlineStr">
+        <is>
+          <t>health services administration</t>
+        </is>
+      </c>
+      <c r="B2828" t="n">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" t="inlineStr">
+        <is>
+          <t>highland scenic highway (liquidation of contract authorization) (trust fund)</t>
+        </is>
+      </c>
+      <c r="B2829" t="n">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" t="inlineStr">
+        <is>
+          <t>highway safety construction programs (liquidation of contract authorization) (trust fund)</t>
+        </is>
+      </c>
+      <c r="B2830" t="n">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" t="inlineStr">
+        <is>
+          <t>highway safety research and development</t>
+        </is>
+      </c>
+      <c r="B2831" t="n">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" t="inlineStr">
+        <is>
+          <t>house leadership offices</t>
+        </is>
+      </c>
+      <c r="B2832" t="n">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" t="inlineStr">
+        <is>
+          <t>human development</t>
+        </is>
+      </c>
+      <c r="B2833" t="n">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" t="inlineStr">
+        <is>
+          <t>indian affairs</t>
+        </is>
+      </c>
+      <c r="B2834" t="n">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" t="inlineStr">
+        <is>
+          <t>indian loan guaranty and insurance fund</t>
+        </is>
+      </c>
+      <c r="B2835" t="n">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" t="inlineStr">
+        <is>
+          <t>international conferences and contingencies
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2836" t="n">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" t="inlineStr">
+        <is>
+          <t>interstate land sales</t>
+        </is>
+      </c>
+      <c r="B2837" t="n">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" t="inlineStr">
+        <is>
+          <t>land and water conservation fund</t>
+        </is>
+      </c>
+      <c r="B2838" t="n">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" t="inlineStr">
+        <is>
+          <t>legislative assistance to senators</t>
+        </is>
+      </c>
+      <c r="B2839" t="n">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" t="inlineStr">
+        <is>
+          <t>limitation on administrative and n0nadmin18trative expenses, federal home loan bank board</t>
+        </is>
+      </c>
+      <c r="B2840" t="n">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" t="inlineStr">
+        <is>
+          <t>limitation on administrative and vocational training expenses, federal prison industries incorporated</t>
+        </is>
+      </c>
+      <c r="B2841" t="n">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" t="inlineStr">
+        <is>
+          <t>limitation on general operating expenses</t>
+        </is>
+      </c>
+      <c r="B2842" t="n">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" t="inlineStr">
+        <is>
+          <t>limitations on availability of revenue</t>
+        </is>
+      </c>
+      <c r="B2843" t="n">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" t="inlineStr">
+        <is>
+          <t>liquidation of contract authorization</t>
+        </is>
+      </c>
+      <c r="B2844" t="n">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" t="inlineStr">
+        <is>
+          <t>lowell historic canal district commission</t>
+        </is>
+      </c>
+      <c r="B2845" t="n">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" t="inlineStr">
+        <is>
+          <t>master plan for future development of the capitol grounds and related areas</t>
+        </is>
+      </c>
+      <c r="B2846" t="n">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" t="inlineStr">
+        <is>
+          <t>micronesian claims fund, trust territory of the pacific islands</t>
+        </is>
+      </c>
+      <c r="B2847" t="n">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" t="inlineStr">
+        <is>
+          <t>middle east special requirements fund</t>
+        </is>
+      </c>
+      <c r="B2848" t="n">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" t="inlineStr">
+        <is>
+          <t>mileage of members</t>
+        </is>
+      </c>
+      <c r="B2849" t="n">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" t="inlineStr">
+        <is>
+          <t>mining enforcement and safety administration</t>
+        </is>
+      </c>
+      <c r="B2850" t="n">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" t="inlineStr">
+        <is>
+          <t>miscellaneous appropriations
+ alaska native fund</t>
+        </is>
+      </c>
+      <c r="B2851" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" t="inlineStr">
+        <is>
+          <t>national agriculturai, library</t>
+        </is>
+      </c>
+      <c r="B2852" t="n">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" t="inlineStr">
+        <is>
+          <t>national archives and record service</t>
+        </is>
+      </c>
+      <c r="B2853" t="n">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" t="inlineStr">
+        <is>
+          <t>national commission on new technological uses of copyrighted works</t>
+        </is>
+      </c>
+      <c r="B2854" t="n">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" t="inlineStr">
+        <is>
+          <t>national fire prevention and control administration</t>
+        </is>
+      </c>
+      <c r="B2855" t="n">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" t="inlineStr">
+        <is>
+          <t>national institute of arthritis, metabolism and digestive diseases</t>
+        </is>
+      </c>
+      <c r="B2856" t="n">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" t="inlineStr">
+        <is>
+          <t>national institutes or health</t>
+        </is>
+      </c>
+      <c r="B2857" t="n">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" t="inlineStr">
+        <is>
+          <t>navajo and hopi relocation commission</t>
+        </is>
+      </c>
+      <c r="B2858" t="n">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" t="inlineStr">
+        <is>
+          <t>off-system roads (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2859" t="n">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" t="inlineStr">
+        <is>
+          <t>office of interstate land sales registration</t>
+        </is>
+      </c>
+      <c r="B2860" t="n">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" t="inlineStr">
+        <is>
+          <t>office of territorial affairs</t>
+        </is>
+      </c>
+      <c r="B2861" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" t="inlineStr">
+        <is>
+          <t>office of the attending physician revolving fund</t>
+        </is>
+      </c>
+      <c r="B2862" t="n">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" t="inlineStr">
+        <is>
+          <t>office of the law revision counsel</t>
+        </is>
+      </c>
+      <c r="B2863" t="n">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" t="inlineStr">
+        <is>
+          <t>office of the special representative for trade negotiations</t>
+        </is>
+      </c>
+      <c r="B2864" t="n">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" t="inlineStr">
+        <is>
+          <t>office of water research and technology</t>
+        </is>
+      </c>
+      <c r="B2865" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" t="inlineStr">
+        <is>
+          <t>office or the legislative counsel of the senate</t>
+        </is>
+      </c>
+      <c r="B2866" t="n">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" t="inlineStr">
+        <is>
+          <t>offshore shrimp fisheries fund</t>
+        </is>
+      </c>
+      <c r="B2867" t="n">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" t="inlineStr">
+        <is>
+          <t>operating expenses, fossil fuels</t>
+        </is>
+      </c>
+      <c r="B2868" t="n">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" t="inlineStr">
+        <is>
+          <t>operations, research, and administration</t>
+        </is>
+      </c>
+      <c r="B2869" t="n">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" t="inlineStr">
+        <is>
+          <t>overseas highway</t>
+        </is>
+      </c>
+      <c r="B2870" t="n">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" t="inlineStr">
+        <is>
+          <t>payment to the alaska railroad revolving fund</t>
+        </is>
+      </c>
+      <c r="B2871" t="n">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" t="inlineStr">
+        <is>
+          <t>payments to the u.s. virgin islands and puerto rico</t>
+        </is>
+      </c>
+      <c r="B2872" t="n">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" t="inlineStr">
+        <is>
+          <t>plant and capital equipment, fossil fuels</t>
+        </is>
+      </c>
+      <c r="B2873" t="n">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" t="inlineStr">
+        <is>
+          <t>pollution fund</t>
+        </is>
+      </c>
+      <c r="B2874" t="n">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" t="inlineStr">
+        <is>
+          <t>pretrial services agencies</t>
+        </is>
+      </c>
+      <c r="B2875" t="n">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" t="inlineStr">
+        <is>
+          <t>privacy protection study commission</t>
+        </is>
+      </c>
+      <c r="B2876" t="n">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" t="inlineStr">
+        <is>
+          <t>production, processing and marketing</t>
+        </is>
+      </c>
+      <c r="B2877" t="n">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" t="inlineStr">
+        <is>
+          <t>public assistance</t>
+        </is>
+      </c>
+      <c r="B2878" t="n">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" t="inlineStr">
+        <is>
+          <t>public lands development roads and trails (liquidation of contract authority)</t>
+        </is>
+      </c>
+      <c r="B2879" t="n">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" t="inlineStr">
+        <is>
+          <t>rail service assistance</t>
+        </is>
+      </c>
+      <c r="B2880" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>rail transportation employment and improvement</t>
+        </is>
+      </c>
+      <c r="B2881" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" t="inlineStr">
+        <is>
+          <t>rail transportation improvement and employment</t>
+        </is>
+      </c>
+      <c r="B2882" t="n">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>railroad research and development</t>
+        </is>
+      </c>
+      <c r="B2883" t="n">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" t="inlineStr">
+        <is>
+          <t>railroad safety
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2884" t="n">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>rehabilitation services</t>
+        </is>
+      </c>
+      <c r="B2885" t="n">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" t="inlineStr">
+        <is>
+          <t>rent supplemental program</t>
+        </is>
+      </c>
+      <c r="B2886" t="n">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>research, development and demonstrations and university research and training</t>
+        </is>
+      </c>
+      <c r="B2887" t="n">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" t="inlineStr">
+        <is>
+          <t>right-of-way revolving fund (liquidation of contract authorization) (trust fund)</t>
+        </is>
+      </c>
+      <c r="B2888" t="n">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>rural community fire protection grants</t>
+        </is>
+      </c>
+      <c r="B2889" t="n">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" t="inlineStr">
+        <is>
+          <t>rural development and protection</t>
+        </is>
+      </c>
+      <c r="B2890" t="n">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>rural development grants</t>
+        </is>
+      </c>
+      <c r="B2891" t="n">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="inlineStr">
+        <is>
+          <t>rural highway-public transportation demonstration program</t>
+        </is>
+      </c>
+      <c r="B2892" t="n">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>salaries and expenses
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2893" t="n">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="inlineStr">
+        <is>
+          <t>salaries and expenses of referees</t>
+        </is>
+      </c>
+      <c r="B2894" t="n">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>salaries and expenses, antitrust division
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2895" t="n">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="inlineStr">
+        <is>
+          <t>salaries and expenses, community planning and development programs</t>
+        </is>
+      </c>
+      <c r="B2896" t="n">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>salaries and expenses, community relations services</t>
+        </is>
+      </c>
+      <c r="B2897" t="n">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="inlineStr">
+        <is>
+          <t>salaries and expenses, general administration
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2898" t="n">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>salaries and expenses, general legal activities
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2899" t="n">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" t="inlineStr">
+        <is>
+          <t>salaries and expenses, housing programs</t>
+        </is>
+      </c>
+      <c r="B2900" t="n">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>salaries and expenses, policy development and research</t>
+        </is>
+      </c>
+      <c r="B2901" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>salaries and expenses, united states attorneys and marshals
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2902" t="n">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>salaries, officers and employees
+ committee employees</t>
+        </is>
+      </c>
+      <c r="B2903" t="n">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>science and technical research</t>
+        </is>
+      </c>
+      <c r="B2904" t="n">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>secretarial offices</t>
+        </is>
+      </c>
+      <c r="B2905" t="n">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="A2906" t="inlineStr">
+        <is>
+          <t>space and facilities, the judiciary</t>
+        </is>
+      </c>
+      <c r="B2906" t="n">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>special assistance to refugees from cambodia and vietnam</t>
+        </is>
+      </c>
+      <c r="B2907" t="n">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="A2908" t="inlineStr">
+        <is>
+          <t>special assistance to refugees from cambodia and vietnam in the united states</t>
+        </is>
+      </c>
+      <c r="B2908" t="n">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>special payment to recipients of certain retirement and survivor benefits</t>
+        </is>
+      </c>
+      <c r="B2909" t="n">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="2910">
+      <c r="A2910" t="inlineStr">
+        <is>
+          <t>special supplemental food program (wic)</t>
+        </is>
+      </c>
+      <c r="B2910" t="n">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="2911">
+      <c r="A2911" t="inlineStr">
+        <is>
+          <t>speedy trial planning</t>
+        </is>
+      </c>
+      <c r="B2911" t="n">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="2912">
+      <c r="A2912" t="inlineStr">
+        <is>
+          <t>state housing finance and development agencies</t>
+        </is>
+      </c>
+      <c r="B2912" t="n">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="2913">
+      <c r="A2913" t="inlineStr">
+        <is>
+          <t>support of united states prisoners
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2913" t="n">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="2914">
+      <c r="A2914" t="inlineStr">
+        <is>
+          <t>temporary study commissions
+ national commission on supplies and shortages</t>
+        </is>
+      </c>
+      <c r="B2914" t="n">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="A2915" t="inlineStr">
+        <is>
+          <t>transportation research activities overseas</t>
+        </is>
+      </c>
+      <c r="B2915" t="n">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="A2916" t="inlineStr">
+        <is>
+          <t>trust fund</t>
+        </is>
+      </c>
+      <c r="B2916" t="n">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="A2917" t="inlineStr">
+        <is>
+          <t>u. s. postal service</t>
+        </is>
+      </c>
+      <c r="B2917" t="n">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="A2918" t="inlineStr">
+        <is>
+          <t>u. s. tax court</t>
+        </is>
+      </c>
+      <c r="B2918" t="n">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="A2919" t="inlineStr">
+        <is>
+          <t>united states-japan friendship activities (foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B2919" t="n">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="2920">
+      <c r="A2920" t="inlineStr">
+        <is>
+          <t>urban mass transportation fund
+ liquidation of contract authorization</t>
+        </is>
+      </c>
+      <c r="B2920" t="n">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" t="inlineStr">
+        <is>
+          <t>(including transfer of funds)
+ housing programs</t>
+        </is>
+      </c>
+      <c r="B2921" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" t="inlineStr">
+        <is>
+          <t>(liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B2922" t="n">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" t="inlineStr">
+        <is>
+          <t>administration expenses</t>
+        </is>
+      </c>
+      <c r="B2923" t="n">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" t="inlineStr">
+        <is>
+          <t>administration on foreign affairs</t>
+        </is>
+      </c>
+      <c r="B2924" t="n">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" t="inlineStr">
+        <is>
+          <t>air forge stock fund</t>
+        </is>
+      </c>
+      <c r="B2925" t="n">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" t="inlineStr">
+        <is>
+          <t>alaska highway</t>
+        </is>
+      </c>
+      <c r="B2926" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="A2927" t="inlineStr">
+        <is>
+          <t>alaska roads study</t>
+        </is>
+      </c>
+      <c r="B2927" t="n">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" t="inlineStr">
+        <is>
+          <t>allowances and expenses</t>
+        </is>
+      </c>
+      <c r="B2928" t="n">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" t="inlineStr">
+        <is>
+          <t>animal ann plant health inspection service</t>
+        </is>
+      </c>
+      <c r="B2929" t="n">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" t="inlineStr">
+        <is>
+          <t>assistance to refugees from the soviet union and other communist countries in eastern europe</t>
+        </is>
+      </c>
+      <c r="B2930" t="n">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" t="inlineStr">
+        <is>
+          <t>assistance to refugees in the united states
+ (cuban program)</t>
+        </is>
+      </c>
+      <c r="B2931" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" t="inlineStr">
+        <is>
+          <t>assistant secretary for health</t>
+        </is>
+      </c>
+      <c r="B2932" t="n">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="A2933" t="inlineStr">
+        <is>
+          <t>automatic elevator operators</t>
+        </is>
+      </c>
+      <c r="B2933" t="n">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" t="inlineStr">
+        <is>
+          <t>baltimore-washington parkway</t>
+        </is>
+      </c>
+      <c r="B2934" t="n">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" t="inlineStr">
+        <is>
+          <t>bicentennial services</t>
+        </is>
+      </c>
+      <c r="B2935" t="n">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" t="inlineStr">
+        <is>
+          <t>botanic gardens</t>
+        </is>
+      </c>
+      <c r="B2936" t="n">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" t="inlineStr">
+        <is>
+          <t>bureau of alcohol, tobacco, and firearms</t>
+        </is>
+      </c>
+      <c r="B2937" t="n">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" t="inlineStr">
+        <is>
+          <t>bureau of economic analysis</t>
+        </is>
+      </c>
+      <c r="B2938" t="n">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2939">
+      <c r="A2939" t="inlineStr">
+        <is>
+          <t>bureau of government financial operations</t>
+        </is>
+      </c>
+      <c r="B2939" t="n">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="2940">
+      <c r="A2940" t="inlineStr">
+        <is>
+          <t>capitol tower plant</t>
+        </is>
+      </c>
+      <c r="B2940" t="n">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="2941">
+      <c r="A2941" t="inlineStr">
+        <is>
+          <t>center for disease control</t>
+        </is>
+      </c>
+      <c r="B2941" t="n">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="2942">
+      <c r="A2942" t="inlineStr">
+        <is>
+          <t>central intelligence agency retirement and disability fund</t>
+        </is>
+      </c>
+      <c r="B2942" t="n">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="2943">
+      <c r="A2943" t="inlineStr">
+        <is>
+          <t>committee for purchase from the blind and other severely handicapped</t>
+        </is>
+      </c>
+      <c r="B2943" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="2944">
+      <c r="A2944" t="inlineStr">
+        <is>
+          <t>commodity credit corporation reimbursement for net realized losses</t>
+        </is>
+      </c>
+      <c r="B2944" t="n">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="2945">
+      <c r="A2945" t="inlineStr">
+        <is>
+          <t>compensation and mileage foe the members</t>
+        </is>
+      </c>
+      <c r="B2945" t="n">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="2946">
+      <c r="A2946" t="inlineStr">
+        <is>
+          <t>compensation and mileage op the vice president and senators and expense allowances of the vice president and leaders of the senate</t>
+        </is>
+      </c>
+      <c r="B2946" t="n">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="2947">
+      <c r="A2947" t="inlineStr">
+        <is>
+          <t>congressional budget office</t>
+        </is>
+      </c>
+      <c r="B2947" t="n">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2948">
+      <c r="A2948" t="inlineStr">
+        <is>
+          <t>conservation
+ soil conservation service</t>
+        </is>
+      </c>
+      <c r="B2948" t="n">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="A2949" t="inlineStr">
+        <is>
+          <t>construction op an extension to the new senate office building</t>
+        </is>
+      </c>
+      <c r="B2949" t="n">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="A2950" t="inlineStr">
+        <is>
+          <t>construction, metropolitan washington airports</t>
+        </is>
+      </c>
+      <c r="B2950" t="n">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>corporation for public broadcasting public broadcasting fund</t>
+        </is>
+      </c>
+      <c r="B2951" t="n">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" t="inlineStr">
+        <is>
+          <t>corps op engineers—civil</t>
+        </is>
+      </c>
+      <c r="B2952" t="n">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>council on wage and price stability</t>
+        </is>
+      </c>
+      <c r="B2953" t="n">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" t="inlineStr">
+        <is>
+          <t>cuban refugee assistance</t>
+        </is>
+      </c>
+      <c r="B2954" t="n">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>defense civil preparedness agency</t>
+        </is>
+      </c>
+      <c r="B2955" t="n">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" t="inlineStr">
+        <is>
+          <t>defense stock fund</t>
+        </is>
+      </c>
+      <c r="B2956" t="n">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>department of defense civil</t>
+        </is>
+      </c>
+      <c r="B2957" t="n">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" t="inlineStr">
+        <is>
+          <t>department of defense, military</t>
+        </is>
+      </c>
+      <c r="B2958" t="n">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>department of defense—civil
+ department of the army</t>
+        </is>
+      </c>
+      <c r="B2959" t="n">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" t="inlineStr">
+        <is>
+          <t>department of housing and urban development
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B2960" t="n">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>economic management support center</t>
+        </is>
+      </c>
+      <c r="B2961" t="n">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" t="inlineStr">
+        <is>
+          <t>educational activities overseas (special foreign curency program)</t>
+        </is>
+      </c>
+      <c r="B2962" t="n">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" t="inlineStr">
+        <is>
+          <t>elderly feeding program</t>
+        </is>
+      </c>
+      <c r="B2963" t="n">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" t="inlineStr">
+        <is>
+          <t>emergency migration and refugee assistance fund</t>
+        </is>
+      </c>
+      <c r="B2964" t="n">
+        <v>2963</v>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="A2965" t="inlineStr">
+        <is>
+          <t>employment and training assistance</t>
+        </is>
+      </c>
+      <c r="B2965" t="n">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" t="inlineStr">
+        <is>
+          <t>export-import bank or the united states</t>
+        </is>
+      </c>
+      <c r="B2966" t="n">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" t="inlineStr">
+        <is>
+          <t>farm income stabilization
+ agricultural, stabilization and conservation service</t>
+        </is>
+      </c>
+      <c r="B2967" t="n">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>federal-aid highways</t>
+        </is>
+      </c>
+      <c r="B2968" t="n">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>financing funds</t>
+        </is>
+      </c>
+      <c r="B2969" t="n">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>foreign assistance
+ international disaster assistance</t>
+        </is>
+      </c>
+      <c r="B2970" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>general management and agency operations</t>
+        </is>
+      </c>
+      <c r="B2971" t="n">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>grants to states for unemployment insurance and employment services</t>
+        </is>
+      </c>
+      <c r="B2972" t="n">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>grants-in-aid for airports (liquidation of contract authorization) (airport and airway trust fund)</t>
+        </is>
+      </c>
+      <c r="B2973" t="n">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>health resources</t>
+        </is>
+      </c>
+      <c r="B2974" t="n">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>health resources administration</t>
+        </is>
+      </c>
+      <c r="B2975" t="n">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>health: services</t>
+        </is>
+      </c>
+      <c r="B2976" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>highway-related safety grants (liquidation of con in act authorization)</t>
+        </is>
+      </c>
+      <c r="B2977" t="n">
+        <v>2976</v>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>highways crossing federal projects</t>
+        </is>
+      </c>
+      <c r="B2978" t="n">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>intelligence community oversight</t>
+        </is>
+      </c>
+      <c r="B2979" t="n">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>international development assistance
+ multilateral assistance
+payment to international fund for agricultural development</t>
+        </is>
+      </c>
+      <c r="B2980" t="n">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>international financial institutions
+ investment in african development fund</t>
+        </is>
+      </c>
+      <c r="B2981" t="n">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>international military education and training</t>
+        </is>
+      </c>
+      <c r="B2982" t="n">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>investment in african development fund</t>
+        </is>
+      </c>
+      <c r="B2983" t="n">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>investment in fund anticipation notes</t>
+        </is>
+      </c>
+      <c r="B2984" t="n">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>joint committee on inaugural ceremonies of 1977</t>
+        </is>
+      </c>
+      <c r="B2985" t="n">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>library of congress james madison memorial building</t>
+        </is>
+      </c>
+      <c r="B2986" t="n">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>limitation on administrative and operating expenses</t>
+        </is>
+      </c>
+      <c r="B2987" t="n">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>local public works program</t>
+        </is>
+      </c>
+      <c r="B2988" t="n">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>military personnel, ant force</t>
+        </is>
+      </c>
+      <c r="B2989" t="n">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>miscellaneous provisions</t>
+        </is>
+      </c>
+      <c r="B2990" t="n">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>mobile home standards program</t>
+        </is>
+      </c>
+      <c r="B2991" t="n">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>national commission on supplies and shortages</t>
+        </is>
+      </c>
+      <c r="B2992" t="n">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>national commission on the observance of international women’s year, 1975</t>
+        </is>
+      </c>
+      <c r="B2993" t="n">
+        <v>2992</v>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>national institute of allergy and infections diseases</t>
+        </is>
+      </c>
+      <c r="B2994" t="n">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>national institute of neurological and communicative disorders and stroke</t>
+        </is>
+      </c>
+      <c r="B2995" t="n">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>national institute of rental research</t>
+        </is>
+      </c>
+      <c r="B2996" t="n">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>national institutes op health</t>
+        </is>
+      </c>
+      <c r="B2997" t="n">
+        <v>2996</v>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>national scenic and recreational highway</t>
+        </is>
+      </c>
+      <c r="B2998" t="n">
+        <v>2997</v>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>national study commission on records and documents of federal officials</t>
+        </is>
+      </c>
+      <c r="B2999" t="n">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>national transportation policy study commission</t>
+        </is>
+      </c>
+      <c r="B3000" t="n">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="inlineStr">
+        <is>
+          <t>naval petroleum reserve</t>
+        </is>
+      </c>
+      <c r="B3001" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="inlineStr">
+        <is>
+          <t>northeast corridor improvement program</t>
+        </is>
+      </c>
+      <c r="B3002" t="n">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="A3003" t="inlineStr">
+        <is>
+          <t>office of drug abuse policy</t>
+        </is>
+      </c>
+      <c r="B3003" t="n">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="A3004" t="inlineStr">
+        <is>
+          <t>office of energy programs</t>
+        </is>
+      </c>
+      <c r="B3004" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="A3005" t="inlineStr">
+        <is>
+          <t>office of preparedness</t>
+        </is>
+      </c>
+      <c r="B3005" t="n">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="A3006" t="inlineStr">
+        <is>
+          <t>office of revenue sharing</t>
+        </is>
+      </c>
+      <c r="B3006" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="A3007" t="inlineStr">
+        <is>
+          <t>office of revenue sharing antirecession financial assistance fund</t>
+        </is>
+      </c>
+      <c r="B3007" t="n">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="A3008" t="inlineStr">
+        <is>
+          <t>office of science and technology policy
+ salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B3008" t="n">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="A3009" t="inlineStr">
+        <is>
+          <t>operating expenses of the agency for international development</t>
+        </is>
+      </c>
+      <c r="B3009" t="n">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="A3010" t="inlineStr">
+        <is>
+          <t>operation and maintenance, air forge reserve</t>
+        </is>
+      </c>
+      <c r="B3010" t="n">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="A3011" t="inlineStr">
+        <is>
+          <t>operation and maintenance, metropolitan washington airports</t>
+        </is>
+      </c>
+      <c r="B3011" t="n">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="A3012" t="inlineStr">
+        <is>
+          <t>operation and maintenance. amur reserve</t>
+        </is>
+      </c>
+      <c r="B3012" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="A3013" t="inlineStr">
+        <is>
+          <t>operation and maintenance. navy reserve</t>
+        </is>
+      </c>
+      <c r="B3013" t="n">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="A3014" t="inlineStr">
+        <is>
+          <t>operation and; maintenance, air force</t>
+        </is>
+      </c>
+      <c r="B3014" t="n">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="inlineStr">
+        <is>
+          <t>operation op the national park system</t>
+        </is>
+      </c>
+      <c r="B3015" t="n">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="inlineStr">
+        <is>
+          <t>other procurement, army, 1972/1974
+ (liquidation of deficiencies)</t>
+        </is>
+      </c>
+      <c r="B3016" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="inlineStr">
+        <is>
+          <t>payment to conditional gut fund, general</t>
+        </is>
+      </c>
+      <c r="B3017" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="inlineStr">
+        <is>
+          <t>payments fob purchase of conrail securities</t>
+        </is>
+      </c>
+      <c r="B3018" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="inlineStr">
+        <is>
+          <t>payments to railroad retirement trust fund</t>
+        </is>
+      </c>
+      <c r="B3019" t="n">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="inlineStr">
+        <is>
+          <t>payments to railroad retirement trust funds</t>
+        </is>
+      </c>
+      <c r="B3020" t="n">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="inlineStr">
+        <is>
+          <t>payments to social security trust and other funds</t>
+        </is>
+      </c>
+      <c r="B3021" t="n">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="inlineStr">
+        <is>
+          <t>petroleum reserves</t>
+        </is>
+      </c>
+      <c r="B3022" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="inlineStr">
+        <is>
+          <t>procurement of ammunition, army, 1973/1975
+ (liquidation of deficiencies)</t>
+        </is>
+      </c>
+      <c r="B3023" t="n">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="inlineStr">
+        <is>
+          <t>procurement of equipment and missiles, army, 1971/1973
+ (liquidation of deficiencies)</t>
+        </is>
+      </c>
+      <c r="B3024" t="n">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="inlineStr">
+        <is>
+          <t>procurement, defense adenoids</t>
+        </is>
+      </c>
+      <c r="B3025" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="inlineStr">
+        <is>
+          <t>production, processing, and marketing</t>
+        </is>
+      </c>
+      <c r="B3026" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="inlineStr">
+        <is>
+          <t>project acceleration demonstration program</t>
+        </is>
+      </c>
+      <c r="B3027" t="n">
+        <v>3026</v>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="inlineStr">
+        <is>
+          <t>projects substituted for interstate system projects</t>
+        </is>
+      </c>
+      <c r="B3028" t="n">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" t="inlineStr">
+        <is>
+          <t>public lands development roads and trails</t>
+        </is>
+      </c>
+      <c r="B3029" t="n">
+        <v>3028</v>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="inlineStr">
+        <is>
+          <t>rail service operating payments</t>
+        </is>
+      </c>
+      <c r="B3030" t="n">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="inlineStr">
+        <is>
+          <t>railroad rehabilitation and improvement</t>
+        </is>
+      </c>
+      <c r="B3031" t="n">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="inlineStr">
+        <is>
+          <t>regional rail transportation protective account</t>
+        </is>
+      </c>
+      <c r="B3032" t="n">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="inlineStr">
+        <is>
+          <t>restoration of facilities on guam, defense</t>
+        </is>
+      </c>
+      <c r="B3033" t="n">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>road construction</t>
+        </is>
+      </c>
+      <c r="B3034" t="n">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="inlineStr">
+        <is>
+          <t>road construction
+ (liquidation op contract authority)</t>
+        </is>
+      </c>
+      <c r="B3035" t="n">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="inlineStr">
+        <is>
+          <t>rural development and protection
+ farmers home administration</t>
+        </is>
+      </c>
+      <c r="B3036" t="n">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="inlineStr">
+        <is>
+          <t>salaries and expenses, u.s. attorneys and marshals</t>
+        </is>
+      </c>
+      <c r="B3037" t="n">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="inlineStr">
+        <is>
+          <t>settlement of claims and sluts</t>
+        </is>
+      </c>
+      <c r="B3038" t="n">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="inlineStr">
+        <is>
+          <t>small business administration
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B3039" t="n">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="inlineStr">
+        <is>
+          <t>special assistance to refugees from cambodia, vietnam, and laos in the united states</t>
+        </is>
+      </c>
+      <c r="B3040" t="n">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="A3041" t="inlineStr">
+        <is>
+          <t>special projects and training</t>
+        </is>
+      </c>
+      <c r="B3041" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="inlineStr">
+        <is>
+          <t>strategic petroleum reserve</t>
+        </is>
+      </c>
+      <c r="B3042" t="n">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="inlineStr">
+        <is>
+          <t>temporary employment assistance</t>
+        </is>
+      </c>
+      <c r="B3043" t="n">
+        <v>3042</v>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="inlineStr">
+        <is>
+          <t>temporary study commission</t>
+        </is>
+      </c>
+      <c r="B3044" t="n">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="inlineStr">
+        <is>
+          <t>territorial highway (liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B3045" t="n">
+        <v>3044</v>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="inlineStr">
+        <is>
+          <t>transportation research activities overseas (special foreign currency program)</t>
+        </is>
+      </c>
+      <c r="B3046" t="n">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="inlineStr">
+        <is>
+          <t>transportation, planning, research, and development</t>
+        </is>
+      </c>
+      <c r="B3047" t="n">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="inlineStr">
+        <is>
+          <t>united states emergency refugee and migration assistance fund</t>
+        </is>
+      </c>
+      <c r="B3048" t="n">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="inlineStr">
+        <is>
+          <t>united states information agency
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B3049" t="n">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="inlineStr">
+        <is>
+          <t>united states postal service</t>
+        </is>
+      </c>
+      <c r="B3050" t="n">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="inlineStr">
+        <is>
+          <t>urban mass transportation administration
+ urban mass transportation fund
+(liquidation of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B3051" t="n">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="inlineStr">
+        <is>
+          <t>urban mass transportation fund
+ rail service operating payments</t>
+        </is>
+      </c>
+      <c r="B3052" t="n">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="inlineStr">
+        <is>
+          <t>very low-income housing repair grants</t>
+        </is>
+      </c>
+      <c r="B3053" t="n">
+        <v>3052</v>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="inlineStr">
+        <is>
+          <t>vocational rehabilitation revolving fund</t>
+        </is>
+      </c>
+      <c r="B3054" t="n">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="inlineStr">
+        <is>
+          <t>water rank program</t>
+        </is>
+      </c>
+      <c r="B3055" t="n">
+        <v>3054</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/processed_output/DivisionMapping.xlsx
+++ b/processed_output/DivisionMapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3055"/>
+  <dimension ref="A1:B3143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31136,6 +31136,889 @@
         <v>3054</v>
       </c>
     </row>
+    <row r="3056">
+      <c r="A3056" t="inlineStr">
+        <is>
+          <t>chapter 1—international monetary fund</t>
+        </is>
+      </c>
+      <c r="B3056" t="n">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="inlineStr">
+        <is>
+          <t>chapter 2.—inter-american development bank</t>
+        </is>
+      </c>
+      <c r="B3057" t="n">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="A3058" t="inlineStr">
+        <is>
+          <t>chapter 3.—annual report of national advisory council</t>
+        </is>
+      </c>
+      <c r="B3058" t="n">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="inlineStr">
+        <is>
+          <t>chapter 4.—audit of exchange stabilization fund</t>
+        </is>
+      </c>
+      <c r="B3059" t="n">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="inlineStr">
+        <is>
+          <t>chapter 5—employee benefits for united states representatives</t>
+        </is>
+      </c>
+      <c r="B3060" t="n">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="inlineStr">
+        <is>
+          <t>administrative provisions 2</t>
+        </is>
+      </c>
+      <c r="B3061" t="n">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="inlineStr">
+        <is>
+          <t>general investigations 2</t>
+        </is>
+      </c>
+      <c r="B3062" t="n">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="inlineStr">
+        <is>
+          <t>operation and maintenance 2</t>
+        </is>
+      </c>
+      <c r="B3063" t="n">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="inlineStr">
+        <is>
+          <t>operation and maintenance 3</t>
+        </is>
+      </c>
+      <c r="B3064" t="n">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="inlineStr">
+        <is>
+          <t>salaries and expenses 2</t>
+        </is>
+      </c>
+      <c r="B3065" t="n">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="inlineStr">
+        <is>
+          <t>salaries and expenses 3</t>
+        </is>
+      </c>
+      <c r="B3066" t="n">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="inlineStr">
+        <is>
+          <t>salaries and expenses 4</t>
+        </is>
+      </c>
+      <c r="B3067" t="n">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="inlineStr">
+        <is>
+          <t>salaries and expenses 5</t>
+        </is>
+      </c>
+      <c r="B3068" t="n">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="inlineStr">
+        <is>
+          <t>salaries and expenses 6</t>
+        </is>
+      </c>
+      <c r="B3069" t="n">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="inlineStr">
+        <is>
+          <t>working capital fund 2</t>
+        </is>
+      </c>
+      <c r="B3070" t="n">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="A3071" t="inlineStr">
+        <is>
+          <t>research and development 2</t>
+        </is>
+      </c>
+      <c r="B3071" t="n">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="inlineStr">
+        <is>
+          <t>hospitals and medical care 2</t>
+        </is>
+      </c>
+      <c r="B3072" t="n">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="inlineStr">
+        <is>
+          <t>part a—vocational education</t>
+        </is>
+      </c>
+      <c r="B3073" t="n">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="inlineStr">
+        <is>
+          <t>part b—extension of national defense education act of 1958</t>
+        </is>
+      </c>
+      <c r="B3074" t="n">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>part c—federally affected areas</t>
+        </is>
+      </c>
+      <c r="B3075" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>administration of territories 2</t>
+        </is>
+      </c>
+      <c r="B3076" t="n">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>administrative provisions 3</t>
+        </is>
+      </c>
+      <c r="B3077" t="n">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>army security agency 2</t>
+        </is>
+      </c>
+      <c r="B3078" t="n">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="inlineStr">
+        <is>
+          <t>construction 2</t>
+        </is>
+      </c>
+      <c r="B3079" t="n">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="inlineStr">
+        <is>
+          <t>construction of mint facilities 2</t>
+        </is>
+      </c>
+      <c r="B3080" t="n">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="inlineStr">
+        <is>
+          <t>special international exhibitions 2</t>
+        </is>
+      </c>
+      <c r="B3081" t="n">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="inlineStr">
+        <is>
+          <t>operation and maintenance, marine corps 2</t>
+        </is>
+      </c>
+      <c r="B3082" t="n">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="inlineStr">
+        <is>
+          <t>general provisions 2</t>
+        </is>
+      </c>
+      <c r="B3083" t="n">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="inlineStr">
+        <is>
+          <t>departmental management 2</t>
+        </is>
+      </c>
+      <c r="B3084" t="n">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="inlineStr">
+        <is>
+          <t>animal and plant health inspection service 2</t>
+        </is>
+      </c>
+      <c r="B3085" t="n">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="inlineStr">
+        <is>
+          <t>acquisition of property as a site for parking facilities for the united states senate</t>
+        </is>
+      </c>
+      <c r="B3086" t="n">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="inlineStr">
+        <is>
+          <t>eisenhower college grants</t>
+        </is>
+      </c>
+      <c r="B3087" t="n">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="inlineStr">
+        <is>
+          <t>environmental impact study on the relocation of the government printing office</t>
+        </is>
+      </c>
+      <c r="B3088" t="n">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="inlineStr">
+        <is>
+          <t>fiscal year 1973 retroactive pay costs</t>
+        </is>
+      </c>
+      <c r="B3089" t="n">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="inlineStr">
+        <is>
+          <t>full deposit insurance study</t>
+        </is>
+      </c>
+      <c r="B3090" t="n">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="inlineStr">
+        <is>
+          <t>funds appropriated to the president
+ federal disaster assistance administration</t>
+        </is>
+      </c>
+      <c r="B3091" t="n">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="inlineStr">
+        <is>
+          <t>high speed ground transportation research and development</t>
+        </is>
+      </c>
+      <c r="B3092" t="n">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="inlineStr">
+        <is>
+          <t>house barber shops revolving fund</t>
+        </is>
+      </c>
+      <c r="B3093" t="n">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="inlineStr">
+        <is>
+          <t>improvement of postsecondary education</t>
+        </is>
+      </c>
+      <c r="B3094" t="n">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="inlineStr">
+        <is>
+          <t>interim operating assistance</t>
+        </is>
+      </c>
+      <c r="B3095" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="inlineStr">
+        <is>
+          <t>national commission on electronic fund transfers</t>
+        </is>
+      </c>
+      <c r="B3096" t="n">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="inlineStr">
+        <is>
+          <t>office of management and budget
+ office of federal procurement policy</t>
+        </is>
+      </c>
+      <c r="B3097" t="n">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="inlineStr">
+        <is>
+          <t>operating-differential subsidies (liquidation op contract authority)</t>
+        </is>
+      </c>
+      <c r="B3098" t="n">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="inlineStr">
+        <is>
+          <t>operation of indian program</t>
+        </is>
+      </c>
+      <c r="B3099" t="n">
+        <v>3098</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="inlineStr">
+        <is>
+          <t>postal service</t>
+        </is>
+      </c>
+      <c r="B3100" t="n">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="inlineStr">
+        <is>
+          <t>real property operations
+ federal buildings fund</t>
+        </is>
+      </c>
+      <c r="B3101" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="inlineStr">
+        <is>
+          <t>reserve forces facilities</t>
+        </is>
+      </c>
+      <c r="B3102" t="n">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="inlineStr">
+        <is>
+          <t>surety bond guarantees fund</t>
+        </is>
+      </c>
+      <c r="B3103" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="inlineStr">
+        <is>
+          <t>surveys, investigations and research</t>
+        </is>
+      </c>
+      <c r="B3104" t="n">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="inlineStr">
+        <is>
+          <t>committee employees 2</t>
+        </is>
+      </c>
+      <c r="B3105" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="inlineStr">
+        <is>
+          <t>disaster loan fund 2</t>
+        </is>
+      </c>
+      <c r="B3106" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="inlineStr">
+        <is>
+          <t>(including transfer of funds) 2</t>
+        </is>
+      </c>
+      <c r="B3107" t="n">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="inlineStr">
+        <is>
+          <t>administrative office of the united states courts 2</t>
+        </is>
+      </c>
+      <c r="B3108" t="n">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="inlineStr">
+        <is>
+          <t>agricultural marketing service 2</t>
+        </is>
+      </c>
+      <c r="B3109" t="n">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="inlineStr">
+        <is>
+          <t>bureau of economic analysis 2</t>
+        </is>
+      </c>
+      <c r="B3110" t="n">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="inlineStr">
+        <is>
+          <t>bureau of the census 2</t>
+        </is>
+      </c>
+      <c r="B3111" t="n">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="inlineStr">
+        <is>
+          <t>council on wage and price stability 2</t>
+        </is>
+      </c>
+      <c r="B3112" t="n">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="inlineStr">
+        <is>
+          <t>court of claims 2</t>
+        </is>
+      </c>
+      <c r="B3113" t="n">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="inlineStr">
+        <is>
+          <t>courts of appeals, district courts, and other judicial services 2</t>
+        </is>
+      </c>
+      <c r="B3114" t="n">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="inlineStr">
+        <is>
+          <t>customs court 2</t>
+        </is>
+      </c>
+      <c r="B3115" t="n">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="inlineStr">
+        <is>
+          <t>defense civil preparedness agency 2</t>
+        </is>
+      </c>
+      <c r="B3116" t="n">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="inlineStr">
+        <is>
+          <t>domestic and international business administration 2</t>
+        </is>
+      </c>
+      <c r="B3117" t="n">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="inlineStr">
+        <is>
+          <t>domestic council 2</t>
+        </is>
+      </c>
+      <c r="B3118" t="n">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="inlineStr">
+        <is>
+          <t>executive residence 2</t>
+        </is>
+      </c>
+      <c r="B3119" t="n">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="inlineStr">
+        <is>
+          <t>federal crop insurance corporation 2</t>
+        </is>
+      </c>
+      <c r="B3120" t="n">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="inlineStr">
+        <is>
+          <t>forest service 2</t>
+        </is>
+      </c>
+      <c r="B3121" t="n">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="inlineStr">
+        <is>
+          <t>general accounting office 2</t>
+        </is>
+      </c>
+      <c r="B3122" t="n">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="inlineStr">
+        <is>
+          <t>general administration 2</t>
+        </is>
+      </c>
+      <c r="B3123" t="n">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="inlineStr">
+        <is>
+          <t>government printing office 2</t>
+        </is>
+      </c>
+      <c r="B3124" t="n">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="inlineStr">
+        <is>
+          <t>house of representatives 2</t>
+        </is>
+      </c>
+      <c r="B3125" t="n">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="inlineStr">
+        <is>
+          <t>joint items 2</t>
+        </is>
+      </c>
+      <c r="B3126" t="n">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="inlineStr">
+        <is>
+          <t>library of congress 2</t>
+        </is>
+      </c>
+      <c r="B3127" t="n">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="inlineStr">
+        <is>
+          <t>maritime administration 2</t>
+        </is>
+      </c>
+      <c r="B3128" t="n">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="inlineStr">
+        <is>
+          <t>military personnel 2</t>
+        </is>
+      </c>
+      <c r="B3129" t="n">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="inlineStr">
+        <is>
+          <t>national fire prevention and control administration 2</t>
+        </is>
+      </c>
+      <c r="B3130" t="n">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="inlineStr">
+        <is>
+          <t>national oceanic and atmospheric administration 2</t>
+        </is>
+      </c>
+      <c r="B3131" t="n">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="inlineStr">
+        <is>
+          <t>national security council 2</t>
+        </is>
+      </c>
+      <c r="B3132" t="n">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="inlineStr">
+        <is>
+          <t>office of energy programs 2</t>
+        </is>
+      </c>
+      <c r="B3133" t="n">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" t="inlineStr">
+        <is>
+          <t>office of management and budget 2</t>
+        </is>
+      </c>
+      <c r="B3134" t="n">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="inlineStr">
+        <is>
+          <t>office of the special representative for trade negotiations 2</t>
+        </is>
+      </c>
+      <c r="B3135" t="n">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="inlineStr">
+        <is>
+          <t>patent and trademark office 2</t>
+        </is>
+      </c>
+      <c r="B3136" t="n">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="inlineStr">
+        <is>
+          <t>research, development, test, and evaluation 2</t>
+        </is>
+      </c>
+      <c r="B3137" t="n">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="inlineStr">
+        <is>
+          <t>salaries and expenses 7</t>
+        </is>
+      </c>
+      <c r="B3138" t="n">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" t="inlineStr">
+        <is>
+          <t>science and technical research 2</t>
+        </is>
+      </c>
+      <c r="B3139" t="n">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" t="inlineStr">
+        <is>
+          <t>senate 2</t>
+        </is>
+      </c>
+      <c r="B3140" t="n">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" t="inlineStr">
+        <is>
+          <t>special assistance to the president 2</t>
+        </is>
+      </c>
+      <c r="B3141" t="n">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" t="inlineStr">
+        <is>
+          <t>supreme court of the united states 2</t>
+        </is>
+      </c>
+      <c r="B3142" t="n">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" t="inlineStr">
+        <is>
+          <t>united states tax court 2</t>
+        </is>
+      </c>
+      <c r="B3143" t="n">
+        <v>3142</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/processed_output/DivisionMapping.xlsx
+++ b/processed_output/DivisionMapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3143"/>
+  <dimension ref="A1:B3149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32019,6 +32019,71 @@
         <v>3142</v>
       </c>
     </row>
+    <row r="3144">
+      <c r="A3144" t="inlineStr">
+        <is>
+          <t>contingent expenses of the senate 2</t>
+        </is>
+      </c>
+      <c r="B3144" t="n">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="inlineStr">
+        <is>
+          <t>chapter i
+department of labor</t>
+        </is>
+      </c>
+      <c r="B3145" t="n">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" t="inlineStr">
+        <is>
+          <t>chapter ii
+veterans administration</t>
+        </is>
+      </c>
+      <c r="B3146" t="n">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="inlineStr">
+        <is>
+          <t>chapter iii
+department of transportation</t>
+        </is>
+      </c>
+      <c r="B3147" t="n">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="inlineStr">
+        <is>
+          <t>chapter iv
+department of agriculture</t>
+        </is>
+      </c>
+      <c r="B3148" t="n">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="inlineStr">
+        <is>
+          <t>chapter v
+department of commerce</t>
+        </is>
+      </c>
+      <c r="B3149" t="n">
+        <v>3148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/processed_output/DivisionMapping.xlsx
+++ b/processed_output/DivisionMapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6943"/>
+  <dimension ref="A1:B7285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71640,6 +71640,3672 @@
         <v>6942</v>
       </c>
     </row>
+    <row r="6944">
+      <c r="A6944" t="inlineStr">
+        <is>
+          <t>mileage and expenses allowances</t>
+        </is>
+      </c>
+      <c r="B6944" t="n">
+        <v>6943</v>
+      </c>
+    </row>
+    <row r="6945">
+      <c r="A6945" t="inlineStr">
+        <is>
+          <t>salaries and expenses (prior year)
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6945" t="n">
+        <v>6944</v>
+      </c>
+    </row>
+    <row r="6946">
+      <c r="A6946" t="inlineStr">
+        <is>
+          <t>(transfer of funds) 6</t>
+        </is>
+      </c>
+      <c r="B6946" t="n">
+        <v>6945</v>
+      </c>
+    </row>
+    <row r="6947">
+      <c r="A6947" t="inlineStr">
+        <is>
+          <t>(transfer of funds) 7</t>
+        </is>
+      </c>
+      <c r="B6947" t="n">
+        <v>6946</v>
+      </c>
+    </row>
+    <row r="6948">
+      <c r="A6948" t="inlineStr">
+        <is>
+          <t>(transfer of funds) 8</t>
+        </is>
+      </c>
+      <c r="B6948" t="n">
+        <v>6947</v>
+      </c>
+    </row>
+    <row r="6949">
+      <c r="A6949" t="inlineStr">
+        <is>
+          <t>1995 special olympics world games</t>
+        </is>
+      </c>
+      <c r="B6949" t="n">
+        <v>6948</v>
+      </c>
+    </row>
+    <row r="6950">
+      <c r="A6950" t="inlineStr">
+        <is>
+          <t>academic research infrastructure</t>
+        </is>
+      </c>
+      <c r="B6950" t="n">
+        <v>6949</v>
+      </c>
+    </row>
+    <row r="6951">
+      <c r="A6951" t="inlineStr">
+        <is>
+          <t>academic research infrastructure
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6951" t="n">
+        <v>6950</v>
+      </c>
+    </row>
+    <row r="6952">
+      <c r="A6952" t="inlineStr">
+        <is>
+          <t>acquisition, construction, and improvements
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B6952" t="n">
+        <v>6951</v>
+      </c>
+    </row>
+    <row r="6953">
+      <c r="A6953" t="inlineStr">
+        <is>
+          <t>administration for children and families
+ children and families services programs</t>
+        </is>
+      </c>
+      <c r="B6953" t="n">
+        <v>6952</v>
+      </c>
+    </row>
+    <row r="6954">
+      <c r="A6954" t="inlineStr">
+        <is>
+          <t>administrative provisions—small business administration</t>
+        </is>
+      </c>
+      <c r="B6954" t="n">
+        <v>6953</v>
+      </c>
+    </row>
+    <row r="6955">
+      <c r="A6955" t="inlineStr">
+        <is>
+          <t>administrative provision—united states information agency</t>
+        </is>
+      </c>
+      <c r="B6955" t="n">
+        <v>6954</v>
+      </c>
+    </row>
+    <row r="6956">
+      <c r="A6956" t="inlineStr">
+        <is>
+          <t>agricultural research service
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B6956" t="n">
+        <v>6955</v>
+      </c>
+    </row>
+    <row r="6957">
+      <c r="A6957" t="inlineStr">
+        <is>
+          <t>alaska pipeline task force
+ (rescission)
+(oil spill liability trust fund)</t>
+        </is>
+      </c>
+      <c r="B6957" t="n">
+        <v>6956</v>
+      </c>
+    </row>
+    <row r="6958">
+      <c r="A6958" t="inlineStr">
+        <is>
+          <t>annual board of education report and budget revision</t>
+        </is>
+      </c>
+      <c r="B6958" t="n">
+        <v>6957</v>
+      </c>
+    </row>
+    <row r="6959">
+      <c r="A6959" t="inlineStr">
+        <is>
+          <t>annual contributions for assisted housing
+ (including rescission and transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B6959" t="n">
+        <v>6958</v>
+      </c>
+    </row>
+    <row r="6960">
+      <c r="A6960" t="inlineStr">
+        <is>
+          <t>armstrong resolution account</t>
+        </is>
+      </c>
+      <c r="B6960" t="n">
+        <v>6959</v>
+      </c>
+    </row>
+    <row r="6961">
+      <c r="A6961" t="inlineStr">
+        <is>
+          <t>assistance for the new independent states of the former soviet union
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6961" t="n">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="6962">
+      <c r="A6962" t="inlineStr">
+        <is>
+          <t>assistance for the renewal of expiring section 8 subsidy contracts
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B6962" t="n">
+        <v>6961</v>
+      </c>
+    </row>
+    <row r="6963">
+      <c r="A6963" t="inlineStr">
+        <is>
+          <t>assistance for the renewal of section 8 subsidy contracts
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6963" t="n">
+        <v>6962</v>
+      </c>
+    </row>
+    <row r="6964">
+      <c r="A6964" t="inlineStr">
+        <is>
+          <t>biomass energy development
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6964" t="n">
+        <v>6963</v>
+      </c>
+    </row>
+    <row r="6965">
+      <c r="A6965" t="inlineStr">
+        <is>
+          <t>border control system modernization</t>
+        </is>
+      </c>
+      <c r="B6965" t="n">
+        <v>6964</v>
+      </c>
+    </row>
+    <row r="6966">
+      <c r="A6966" t="inlineStr">
+        <is>
+          <t>buying power maintenance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6966" t="n">
+        <v>6965</v>
+      </c>
+    </row>
+    <row r="6967">
+      <c r="A6967" t="inlineStr">
+        <is>
+          <t>cash reserve fund</t>
+        </is>
+      </c>
+      <c r="B6967" t="n">
+        <v>6966</v>
+      </c>
+    </row>
+    <row r="6968">
+      <c r="A6968" t="inlineStr">
+        <is>
+          <t>cash reserve fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6968" t="n">
+        <v>6967</v>
+      </c>
+    </row>
+    <row r="6969">
+      <c r="A6969" t="inlineStr">
+        <is>
+          <t>civil liberties public education fund</t>
+        </is>
+      </c>
+      <c r="B6969" t="n">
+        <v>6968</v>
+      </c>
+    </row>
+    <row r="6970">
+      <c r="A6970" t="inlineStr">
+        <is>
+          <t>commodity supplemental food program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6970" t="n">
+        <v>6969</v>
+      </c>
+    </row>
+    <row r="6971">
+      <c r="A6971" t="inlineStr">
+        <is>
+          <t>community development grants
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B6971" t="n">
+        <v>6970</v>
+      </c>
+    </row>
+    <row r="6972">
+      <c r="A6972" t="inlineStr">
+        <is>
+          <t>community management account</t>
+        </is>
+      </c>
+      <c r="B6972" t="n">
+        <v>6971</v>
+      </c>
+    </row>
+    <row r="6973">
+      <c r="A6973" t="inlineStr">
+        <is>
+          <t>community policing</t>
+        </is>
+      </c>
+      <c r="B6973" t="n">
+        <v>6972</v>
+      </c>
+    </row>
+    <row r="6974">
+      <c r="A6974" t="inlineStr">
+        <is>
+          <t>construction of facilities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6974" t="n">
+        <v>6973</v>
+      </c>
+    </row>
+    <row r="6975">
+      <c r="A6975" t="inlineStr">
+        <is>
+          <t>construction program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6975" t="n">
+        <v>6974</v>
+      </c>
+    </row>
+    <row r="6976">
+      <c r="A6976" t="inlineStr">
+        <is>
+          <t>construction, general
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6976" t="n">
+        <v>6975</v>
+      </c>
+    </row>
+    <row r="6977">
+      <c r="A6977" t="inlineStr">
+        <is>
+          <t>contingent expenses of the senate
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6977" t="n">
+        <v>6976</v>
+      </c>
+    </row>
+    <row r="6978">
+      <c r="A6978" t="inlineStr">
+        <is>
+          <t>contribution to the international bank for reconstruction and development
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6978" t="n">
+        <v>6977</v>
+      </c>
+    </row>
+    <row r="6979">
+      <c r="A6979" t="inlineStr">
+        <is>
+          <t>cooperative state research service
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B6979" t="n">
+        <v>6978</v>
+      </c>
+    </row>
+    <row r="6980">
+      <c r="A6980" t="inlineStr">
+        <is>
+          <t>corporation for national and community service
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6980" t="n">
+        <v>6979</v>
+      </c>
+    </row>
+    <row r="6981">
+      <c r="A6981" t="inlineStr">
+        <is>
+          <t>d.c. general hospital deficit payment</t>
+        </is>
+      </c>
+      <c r="B6981" t="n">
+        <v>6980</v>
+      </c>
+    </row>
+    <row r="6982">
+      <c r="A6982" t="inlineStr">
+        <is>
+          <t>d.c. general hospital deficit payment
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6982" t="n">
+        <v>6981</v>
+      </c>
+    </row>
+    <row r="6983">
+      <c r="A6983" t="inlineStr">
+        <is>
+          <t>defender services
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6983" t="n">
+        <v>6982</v>
+      </c>
+    </row>
+    <row r="6984">
+      <c r="A6984" t="inlineStr">
+        <is>
+          <t>defense business operations fund</t>
+        </is>
+      </c>
+      <c r="B6984" t="n">
+        <v>6983</v>
+      </c>
+    </row>
+    <row r="6985">
+      <c r="A6985" t="inlineStr">
+        <is>
+          <t>department of defense—civil cemeterial expenses, army</t>
+        </is>
+      </c>
+      <c r="B6985" t="n">
+        <v>6984</v>
+      </c>
+    </row>
+    <row r="6986">
+      <c r="A6986" t="inlineStr">
+        <is>
+          <t>department of education
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6986" t="n">
+        <v>6985</v>
+      </c>
+    </row>
+    <row r="6987">
+      <c r="A6987" t="inlineStr">
+        <is>
+          <t>department of health and human services
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6987" t="n">
+        <v>6986</v>
+      </c>
+    </row>
+    <row r="6988">
+      <c r="A6988" t="inlineStr">
+        <is>
+          <t>department of labor
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6988" t="n">
+        <v>6987</v>
+      </c>
+    </row>
+    <row r="6989">
+      <c r="A6989" t="inlineStr">
+        <is>
+          <t>development assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6989" t="n">
+        <v>6988</v>
+      </c>
+    </row>
+    <row r="6990">
+      <c r="A6990" t="inlineStr">
+        <is>
+          <t>direct loan program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B6990" t="n">
+        <v>6989</v>
+      </c>
+    </row>
+    <row r="6991">
+      <c r="A6991" t="inlineStr">
+        <is>
+          <t>disaster assistance</t>
+        </is>
+      </c>
+      <c r="B6991" t="n">
+        <v>6990</v>
+      </c>
+    </row>
+    <row r="6992">
+      <c r="A6992" t="inlineStr">
+        <is>
+          <t>drug courts</t>
+        </is>
+      </c>
+      <c r="B6992" t="n">
+        <v>6991</v>
+      </c>
+    </row>
+    <row r="6993">
+      <c r="A6993" t="inlineStr">
+        <is>
+          <t>economics and statistics administration revolving fund</t>
+        </is>
+      </c>
+      <c r="B6993" t="n">
+        <v>6992</v>
+      </c>
+    </row>
+    <row r="6994">
+      <c r="A6994" t="inlineStr">
+        <is>
+          <t>education loan fund program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B6994" t="n">
+        <v>6993</v>
+      </c>
+    </row>
+    <row r="6995">
+      <c r="A6995" t="inlineStr">
+        <is>
+          <t>educational and cultural exchange programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6995" t="n">
+        <v>6994</v>
+      </c>
+    </row>
+    <row r="6996">
+      <c r="A6996" t="inlineStr">
+        <is>
+          <t>energy supply research and development activities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6996" t="n">
+        <v>6995</v>
+      </c>
+    </row>
+    <row r="6997">
+      <c r="A6997" t="inlineStr">
+        <is>
+          <t>expenses of transportation audit contracts and contract administration</t>
+        </is>
+      </c>
+      <c r="B6997" t="n">
+        <v>6996</v>
+      </c>
+    </row>
+    <row r="6998">
+      <c r="A6998" t="inlineStr">
+        <is>
+          <t>extension service
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B6998" t="n">
+        <v>6997</v>
+      </c>
+    </row>
+    <row r="6999">
+      <c r="A6999" t="inlineStr">
+        <is>
+          <t>facilities and equipment
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B6999" t="n">
+        <v>6998</v>
+      </c>
+    </row>
+    <row r="7000">
+      <c r="A7000" t="inlineStr">
+        <is>
+          <t>facilities, planning and construction</t>
+        </is>
+      </c>
+      <c r="B7000" t="n">
+        <v>6999</v>
+      </c>
+    </row>
+    <row r="7001">
+      <c r="A7001" t="inlineStr">
+        <is>
+          <t>federal buildings fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7001" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="7002">
+      <c r="A7002" t="inlineStr">
+        <is>
+          <t>federal direct student loan program account</t>
+        </is>
+      </c>
+      <c r="B7002" t="n">
+        <v>7001</v>
+      </c>
+    </row>
+    <row r="7003">
+      <c r="A7003" t="inlineStr">
+        <is>
+          <t>federal emergency management agencies</t>
+        </is>
+      </c>
+      <c r="B7003" t="n">
+        <v>7002</v>
+      </c>
+    </row>
+    <row r="7004">
+      <c r="A7004" t="inlineStr">
+        <is>
+          <t>federal-aid highways emergency relief program
+ (highway trust fund)</t>
+        </is>
+      </c>
+      <c r="B7004" t="n">
+        <v>7003</v>
+      </c>
+    </row>
+    <row r="7005">
+      <c r="A7005" t="inlineStr">
+        <is>
+          <t>fha—mutual mortgage insurance program account</t>
+        </is>
+      </c>
+      <c r="B7005" t="n">
+        <v>7004</v>
+      </c>
+    </row>
+    <row r="7006">
+      <c r="A7006" t="inlineStr">
+        <is>
+          <t>financial reporting</t>
+        </is>
+      </c>
+      <c r="B7006" t="n">
+        <v>7005</v>
+      </c>
+    </row>
+    <row r="7007">
+      <c r="A7007" t="inlineStr">
+        <is>
+          <t>foreign military financing program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7007" t="n">
+        <v>7006</v>
+      </c>
+    </row>
+    <row r="7008">
+      <c r="A7008" t="inlineStr">
+        <is>
+          <t>gang resistance education and training</t>
+        </is>
+      </c>
+      <c r="B7008" t="n">
+        <v>7007</v>
+      </c>
+    </row>
+    <row r="7009">
+      <c r="A7009" t="inlineStr">
+        <is>
+          <t>general investigations
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7009" t="n">
+        <v>7008</v>
+      </c>
+    </row>
+    <row r="7010">
+      <c r="A7010" t="inlineStr">
+        <is>
+          <t>general provisions—chapter 3</t>
+        </is>
+      </c>
+      <c r="B7010" t="n">
+        <v>7009</v>
+      </c>
+    </row>
+    <row r="7011">
+      <c r="A7011" t="inlineStr">
+        <is>
+          <t>general provision—department of the treasury</t>
+        </is>
+      </c>
+      <c r="B7011" t="n">
+        <v>7010</v>
+      </c>
+    </row>
+    <row r="7012">
+      <c r="A7012" t="inlineStr">
+        <is>
+          <t>general services administration federal buildings fund</t>
+        </is>
+      </c>
+      <c r="B7012" t="n">
+        <v>7011</v>
+      </c>
+    </row>
+    <row r="7013">
+      <c r="A7013" t="inlineStr">
+        <is>
+          <t>general services administration—general provisions</t>
+        </is>
+      </c>
+      <c r="B7013" t="n">
+        <v>7012</v>
+      </c>
+    </row>
+    <row r="7014">
+      <c r="A7014" t="inlineStr">
+        <is>
+          <t>grants to combat violent crimes against women</t>
+        </is>
+      </c>
+      <c r="B7014" t="n">
+        <v>7013</v>
+      </c>
+    </row>
+    <row r="7015">
+      <c r="A7015" t="inlineStr">
+        <is>
+          <t>grants-in-aid for airports
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7015" t="n">
+        <v>7014</v>
+      </c>
+    </row>
+    <row r="7016">
+      <c r="A7016" t="inlineStr">
+        <is>
+          <t>highway-related safety grants
+ (liquidation of contract authorization)
+(highway trust fund)
+(including rescission and transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7016" t="n">
+        <v>7015</v>
+      </c>
+    </row>
+    <row r="7017">
+      <c r="A7017" t="inlineStr">
+        <is>
+          <t>homeownership and opportunity for people everywhere grants (hope grants)
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7017" t="n">
+        <v>7016</v>
+      </c>
+    </row>
+    <row r="7018">
+      <c r="A7018" t="inlineStr">
+        <is>
+          <t>homeownership assistance
+ (including rescission of funds)</t>
+        </is>
+      </c>
+      <c r="B7018" t="n">
+        <v>7017</v>
+      </c>
+    </row>
+    <row r="7019">
+      <c r="A7019" t="inlineStr">
+        <is>
+          <t>independent audit of retirement board</t>
+        </is>
+      </c>
+      <c r="B7019" t="n">
+        <v>7018</v>
+      </c>
+    </row>
+    <row r="7020">
+      <c r="A7020" t="inlineStr">
+        <is>
+          <t>information resources management service information technology fund</t>
+        </is>
+      </c>
+      <c r="B7020" t="n">
+        <v>7019</v>
+      </c>
+    </row>
+    <row r="7021">
+      <c r="A7021" t="inlineStr">
+        <is>
+          <t>inspection and weighing services
+ limitation on inspection and weighing service expenses</t>
+        </is>
+      </c>
+      <c r="B7021" t="n">
+        <v>7020</v>
+      </c>
+    </row>
+    <row r="7022">
+      <c r="A7022" t="inlineStr">
+        <is>
+          <t>interest payments and repayments of principal</t>
+        </is>
+      </c>
+      <c r="B7022" t="n">
+        <v>7021</v>
+      </c>
+    </row>
+    <row r="7023">
+      <c r="A7023" t="inlineStr">
+        <is>
+          <t>international forestry</t>
+        </is>
+      </c>
+      <c r="B7023" t="n">
+        <v>7022</v>
+      </c>
+    </row>
+    <row r="7024">
+      <c r="A7024" t="inlineStr">
+        <is>
+          <t>job opportunities and basic skills</t>
+        </is>
+      </c>
+      <c r="B7024" t="n">
+        <v>7023</v>
+      </c>
+    </row>
+    <row r="7025">
+      <c r="A7025" t="inlineStr">
+        <is>
+          <t>job-producing economic development incentives</t>
+        </is>
+      </c>
+      <c r="B7025" t="n">
+        <v>7024</v>
+      </c>
+    </row>
+    <row r="7026">
+      <c r="A7026" t="inlineStr">
+        <is>
+          <t>john f. kennedy assassination records review board
+ salaries and expenses</t>
+        </is>
+      </c>
+      <c r="B7026" t="n">
+        <v>7025</v>
+      </c>
+    </row>
+    <row r="7027">
+      <c r="A7027" t="inlineStr">
+        <is>
+          <t>kaho'olawe island conveyance, remediation, and environmental restoration trust fund</t>
+        </is>
+      </c>
+      <c r="B7027" t="n">
+        <v>7026</v>
+      </c>
+    </row>
+    <row r="7028">
+      <c r="A7028" t="inlineStr">
+        <is>
+          <t>land acquisition
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7028" t="n">
+        <v>7027</v>
+      </c>
+    </row>
+    <row r="7029">
+      <c r="A7029" t="inlineStr">
+        <is>
+          <t>library of congress
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7029" t="n">
+        <v>7028</v>
+      </c>
+    </row>
+    <row r="7030">
+      <c r="A7030" t="inlineStr">
+        <is>
+          <t>limitation on administrative expenses
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7030" t="n">
+        <v>7029</v>
+      </c>
+    </row>
+    <row r="7031">
+      <c r="A7031" t="inlineStr">
+        <is>
+          <t>limitations on availability of revenue
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7031" t="n">
+        <v>7030</v>
+      </c>
+    </row>
+    <row r="7032">
+      <c r="A7032" t="inlineStr">
+        <is>
+          <t>limitations on full-time equivalent positions</t>
+        </is>
+      </c>
+      <c r="B7032" t="n">
+        <v>7031</v>
+      </c>
+    </row>
+    <row r="7033">
+      <c r="A7033" t="inlineStr">
+        <is>
+          <t>loan guaranty program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7033" t="n">
+        <v>7032</v>
+      </c>
+    </row>
+    <row r="7034">
+      <c r="A7034" t="inlineStr">
+        <is>
+          <t>local technical assistance and planning grants</t>
+        </is>
+      </c>
+      <c r="B7034" t="n">
+        <v>7033</v>
+      </c>
+    </row>
+    <row r="7035">
+      <c r="A7035" t="inlineStr">
+        <is>
+          <t>low income home energy assistance
+ (including rescission)</t>
+        </is>
+      </c>
+      <c r="B7035" t="n">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="7036">
+      <c r="A7036" t="inlineStr">
+        <is>
+          <t>management funds</t>
+        </is>
+      </c>
+      <c r="B7036" t="n">
+        <v>7035</v>
+      </c>
+    </row>
+    <row r="7037">
+      <c r="A7037" t="inlineStr">
+        <is>
+          <t>marketing services
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7037" t="n">
+        <v>7036</v>
+      </c>
+    </row>
+    <row r="7038">
+      <c r="A7038" t="inlineStr">
+        <is>
+          <t>materials support and other defense programs</t>
+        </is>
+      </c>
+      <c r="B7038" t="n">
+        <v>7037</v>
+      </c>
+    </row>
+    <row r="7039">
+      <c r="A7039" t="inlineStr">
+        <is>
+          <t>military assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7039" t="n">
+        <v>7038</v>
+      </c>
+    </row>
+    <row r="7040">
+      <c r="A7040" t="inlineStr">
+        <is>
+          <t>military construction
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7040" t="n">
+        <v>7039</v>
+      </c>
+    </row>
+    <row r="7041">
+      <c r="A7041" t="inlineStr">
+        <is>
+          <t>municipal fish wharf</t>
+        </is>
+      </c>
+      <c r="B7041" t="n">
+        <v>7040</v>
+      </c>
+    </row>
+    <row r="7042">
+      <c r="A7042" t="inlineStr">
+        <is>
+          <t>national aeronautical facilities
+ (including rescission)</t>
+        </is>
+      </c>
+      <c r="B7042" t="n">
+        <v>7041</v>
+      </c>
+    </row>
+    <row r="7043">
+      <c r="A7043" t="inlineStr">
+        <is>
+          <t>national and community service programs operating expenses
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7043" t="n">
+        <v>7042</v>
+      </c>
+    </row>
+    <row r="7044">
+      <c r="A7044" t="inlineStr">
+        <is>
+          <t>national archives trust fund</t>
+        </is>
+      </c>
+      <c r="B7044" t="n">
+        <v>7043</v>
+      </c>
+    </row>
+    <row r="7045">
+      <c r="A7045" t="inlineStr">
+        <is>
+          <t>national biological survey</t>
+        </is>
+      </c>
+      <c r="B7045" t="n">
+        <v>7044</v>
+      </c>
+    </row>
+    <row r="7046">
+      <c r="A7046" t="inlineStr">
+        <is>
+          <t>national defense sealift fund
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7046" t="n">
+        <v>7045</v>
+      </c>
+    </row>
+    <row r="7047">
+      <c r="A7047" t="inlineStr">
+        <is>
+          <t>national homeownership trust demonstration program</t>
+        </is>
+      </c>
+      <c r="B7047" t="n">
+        <v>7046</v>
+      </c>
+    </row>
+    <row r="7048">
+      <c r="A7048" t="inlineStr">
+        <is>
+          <t>national science foundation headquarters relocation</t>
+        </is>
+      </c>
+      <c r="B7048" t="n">
+        <v>7047</v>
+      </c>
+    </row>
+    <row r="7049">
+      <c r="A7049" t="inlineStr">
+        <is>
+          <t>national service initiative</t>
+        </is>
+      </c>
+      <c r="B7049" t="n">
+        <v>7048</v>
+      </c>
+    </row>
+    <row r="7050">
+      <c r="A7050" t="inlineStr">
+        <is>
+          <t>native american veteran housing loan program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7050" t="n">
+        <v>7049</v>
+      </c>
+    </row>
+    <row r="7051">
+      <c r="A7051" t="inlineStr">
+        <is>
+          <t>new diplomatic posts
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7051" t="n">
+        <v>7050</v>
+      </c>
+    </row>
+    <row r="7052">
+      <c r="A7052" t="inlineStr">
+        <is>
+          <t>next generation high speed rail</t>
+        </is>
+      </c>
+      <c r="B7052" t="n">
+        <v>7051</v>
+      </c>
+    </row>
+    <row r="7053">
+      <c r="A7053" t="inlineStr">
+        <is>
+          <t>north/south center
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7053" t="n">
+        <v>7052</v>
+      </c>
+    </row>
+    <row r="7054">
+      <c r="A7054" t="inlineStr">
+        <is>
+          <t>office of aids research
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7054" t="n">
+        <v>7053</v>
+      </c>
+    </row>
+    <row r="7055">
+      <c r="A7055" t="inlineStr">
+        <is>
+          <t>office of the american workplace</t>
+        </is>
+      </c>
+      <c r="B7055" t="n">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="7056">
+      <c r="A7056" t="inlineStr">
+        <is>
+          <t>office of the assistant secretary for health
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7056" t="n">
+        <v>7055</v>
+      </c>
+    </row>
+    <row r="7057">
+      <c r="A7057" t="inlineStr">
+        <is>
+          <t>oil spill response
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7057" t="n">
+        <v>7056</v>
+      </c>
+    </row>
+    <row r="7058">
+      <c r="A7058" t="inlineStr">
+        <is>
+          <t>operating expenses
+ (transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7058" t="n">
+        <v>7057</v>
+      </c>
+    </row>
+    <row r="7059">
+      <c r="A7059" t="inlineStr">
+        <is>
+          <t>operations
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7059" t="n">
+        <v>7058</v>
+      </c>
+    </row>
+    <row r="7060">
+      <c r="A7060" t="inlineStr">
+        <is>
+          <t>optical and dental benefits
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7060" t="n">
+        <v>7059</v>
+      </c>
+    </row>
+    <row r="7061">
+      <c r="A7061" t="inlineStr">
+        <is>
+          <t>ounce of prevention council</t>
+        </is>
+      </c>
+      <c r="B7061" t="n">
+        <v>7060</v>
+      </c>
+    </row>
+    <row r="7062">
+      <c r="A7062" t="inlineStr">
+        <is>
+          <t>pay adjustment</t>
+        </is>
+      </c>
+      <c r="B7062" t="n">
+        <v>7061</v>
+      </c>
+    </row>
+    <row r="7063">
+      <c r="A7063" t="inlineStr">
+        <is>
+          <t>payments to air carriers
+ (liquidation of contract authorization)
+(airport and airway trust fund)
+(including rescission of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B7063" t="n">
+        <v>7062</v>
+      </c>
+    </row>
+    <row r="7064">
+      <c r="A7064" t="inlineStr">
+        <is>
+          <t>payments to states and possessions
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7064" t="n">
+        <v>7063</v>
+      </c>
+    </row>
+    <row r="7065">
+      <c r="A7065" t="inlineStr">
+        <is>
+          <t>payments to the postal service</t>
+        </is>
+      </c>
+      <c r="B7065" t="n">
+        <v>7064</v>
+      </c>
+    </row>
+    <row r="7066">
+      <c r="A7066" t="inlineStr">
+        <is>
+          <t>payments to widows and heirs of deceased</t>
+        </is>
+      </c>
+      <c r="B7066" t="n">
+        <v>7065</v>
+      </c>
+    </row>
+    <row r="7067">
+      <c r="A7067" t="inlineStr">
+        <is>
+          <t>pennsylvania station redevelopment project</t>
+        </is>
+      </c>
+      <c r="B7067" t="n">
+        <v>7066</v>
+      </c>
+    </row>
+    <row r="7068">
+      <c r="A7068" t="inlineStr">
+        <is>
+          <t>permanent appropriations</t>
+        </is>
+      </c>
+      <c r="B7068" t="n">
+        <v>7067</v>
+      </c>
+    </row>
+    <row r="7069">
+      <c r="A7069" t="inlineStr">
+        <is>
+          <t>procurement, defense-wide
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7069" t="n">
+        <v>7068</v>
+      </c>
+    </row>
+    <row r="7070">
+      <c r="A7070" t="inlineStr">
+        <is>
+          <t>public broadcasting</t>
+        </is>
+      </c>
+      <c r="B7070" t="n">
+        <v>7069</v>
+      </c>
+    </row>
+    <row r="7071">
+      <c r="A7071" t="inlineStr">
+        <is>
+          <t>public law 480 program account
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7071" t="n">
+        <v>7070</v>
+      </c>
+    </row>
+    <row r="7072">
+      <c r="A7072" t="inlineStr">
+        <is>
+          <t>public law 480 program accounts</t>
+        </is>
+      </c>
+      <c r="B7072" t="n">
+        <v>7071</v>
+      </c>
+    </row>
+    <row r="7073">
+      <c r="A7073" t="inlineStr">
+        <is>
+          <t>purchase of american-made equipment and products</t>
+        </is>
+      </c>
+      <c r="B7073" t="n">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="7074">
+      <c r="A7074" t="inlineStr">
+        <is>
+          <t>purchase of americanmade equipment and products</t>
+        </is>
+      </c>
+      <c r="B7074" t="n">
+        <v>7073</v>
+      </c>
+    </row>
+    <row r="7075">
+      <c r="A7075" t="inlineStr">
+        <is>
+          <t>radio construction
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7075" t="n">
+        <v>7074</v>
+      </c>
+    </row>
+    <row r="7076">
+      <c r="A7076" t="inlineStr">
+        <is>
+          <t>radio free asia</t>
+        </is>
+      </c>
+      <c r="B7076" t="n">
+        <v>7075</v>
+      </c>
+    </row>
+    <row r="7077">
+      <c r="A7077" t="inlineStr">
+        <is>
+          <t>rainy day fund</t>
+        </is>
+      </c>
+      <c r="B7077" t="n">
+        <v>7076</v>
+      </c>
+    </row>
+    <row r="7078">
+      <c r="A7078" t="inlineStr">
+        <is>
+          <t>rea economic development loans program account</t>
+        </is>
+      </c>
+      <c r="B7078" t="n">
+        <v>7077</v>
+      </c>
+    </row>
+    <row r="7079">
+      <c r="A7079" t="inlineStr">
+        <is>
+          <t>reduction of funding</t>
+        </is>
+      </c>
+      <c r="B7079" t="n">
+        <v>7078</v>
+      </c>
+    </row>
+    <row r="7080">
+      <c r="A7080" t="inlineStr">
+        <is>
+          <t>research and related activities
+ (including transfer and rescission of funds)</t>
+        </is>
+      </c>
+      <c r="B7080" t="n">
+        <v>7079</v>
+      </c>
+    </row>
+    <row r="7081">
+      <c r="A7081" t="inlineStr">
+        <is>
+          <t>research, development, test and evaluation, defense-wide
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7081" t="n">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="7082">
+      <c r="A7082" t="inlineStr">
+        <is>
+          <t>research, inventories, and surveys</t>
+        </is>
+      </c>
+      <c r="B7082" t="n">
+        <v>7081</v>
+      </c>
+    </row>
+    <row r="7083">
+      <c r="A7083" t="inlineStr">
+        <is>
+          <t>restriction on funding united states military personnel in somalia</t>
+        </is>
+      </c>
+      <c r="B7083" t="n">
+        <v>7082</v>
+      </c>
+    </row>
+    <row r="7084">
+      <c r="A7084" t="inlineStr">
+        <is>
+          <t>right-of-way revolving fund
+ (highway trust fund)
+(rescission)</t>
+        </is>
+      </c>
+      <c r="B7084" t="n">
+        <v>7083</v>
+      </c>
+    </row>
+    <row r="7085">
+      <c r="A7085" t="inlineStr">
+        <is>
+          <t>rivers and harbors contributed funds</t>
+        </is>
+      </c>
+      <c r="B7085" t="n">
+        <v>7084</v>
+      </c>
+    </row>
+    <row r="7086">
+      <c r="A7086" t="inlineStr">
+        <is>
+          <t>rural business enterprise grants</t>
+        </is>
+      </c>
+      <c r="B7086" t="n">
+        <v>7085</v>
+      </c>
+    </row>
+    <row r="7087">
+      <c r="A7087" t="inlineStr">
+        <is>
+          <t>rural development administration</t>
+        </is>
+      </c>
+      <c r="B7087" t="n">
+        <v>7086</v>
+      </c>
+    </row>
+    <row r="7088">
+      <c r="A7088" t="inlineStr">
+        <is>
+          <t>rural development administration and farmers home administration</t>
+        </is>
+      </c>
+      <c r="B7088" t="n">
+        <v>7087</v>
+      </c>
+    </row>
+    <row r="7089">
+      <c r="A7089" t="inlineStr">
+        <is>
+          <t>rural development loan fund program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7089" t="n">
+        <v>7088</v>
+      </c>
+    </row>
+    <row r="7090">
+      <c r="A7090" t="inlineStr">
+        <is>
+          <t>rural electrification and telephone loans program account
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7090" t="n">
+        <v>7089</v>
+      </c>
+    </row>
+    <row r="7091">
+      <c r="A7091" t="inlineStr">
+        <is>
+          <t>rural housing insurance fund program account
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7091" t="n">
+        <v>7090</v>
+      </c>
+    </row>
+    <row r="7092">
+      <c r="A7092" t="inlineStr">
+        <is>
+          <t>rural housing voucher program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7092" t="n">
+        <v>7091</v>
+      </c>
+    </row>
+    <row r="7093">
+      <c r="A7093" t="inlineStr">
+        <is>
+          <t>rural technology and cooperative development grants</t>
+        </is>
+      </c>
+      <c r="B7093" t="n">
+        <v>7092</v>
+      </c>
+    </row>
+    <row r="7094">
+      <c r="A7094" t="inlineStr">
+        <is>
+          <t>rural water and waste disposal grants
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7094" t="n">
+        <v>7093</v>
+      </c>
+    </row>
+    <row r="7095">
+      <c r="A7095" t="inlineStr">
+        <is>
+          <t>rural water and waste disposal grants 2</t>
+        </is>
+      </c>
+      <c r="B7095" t="n">
+        <v>7094</v>
+      </c>
+    </row>
+    <row r="7096">
+      <c r="A7096" t="inlineStr">
+        <is>
+          <t>salaries and expenses
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7096" t="n">
+        <v>7095</v>
+      </c>
+    </row>
+    <row r="7097">
+      <c r="A7097" t="inlineStr">
+        <is>
+          <t>salaries and expenses, general legal activities 2</t>
+        </is>
+      </c>
+      <c r="B7097" t="n">
+        <v>7096</v>
+      </c>
+    </row>
+    <row r="7098">
+      <c r="A7098" t="inlineStr">
+        <is>
+          <t>science, aeronautics and technology
+ (including rescission of funds)</t>
+        </is>
+      </c>
+      <c r="B7098" t="n">
+        <v>7097</v>
+      </c>
+    </row>
+    <row r="7099">
+      <c r="A7099" t="inlineStr">
+        <is>
+          <t>scientific activities overseas (foreign currency program)
+ limitation on administrative expenses</t>
+        </is>
+      </c>
+      <c r="B7099" t="n">
+        <v>7098</v>
+      </c>
+    </row>
+    <row r="7100">
+      <c r="A7100" t="inlineStr">
+        <is>
+          <t>severance pay</t>
+        </is>
+      </c>
+      <c r="B7100" t="n">
+        <v>7099</v>
+      </c>
+    </row>
+    <row r="7101">
+      <c r="A7101" t="inlineStr">
+        <is>
+          <t>severely distressed public housing</t>
+        </is>
+      </c>
+      <c r="B7101" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="7102">
+      <c r="A7102" t="inlineStr">
+        <is>
+          <t>short-term borrowing</t>
+        </is>
+      </c>
+      <c r="B7102" t="n">
+        <v>7101</v>
+      </c>
+    </row>
+    <row r="7103">
+      <c r="A7103" t="inlineStr">
+        <is>
+          <t>space flight, control, and data communications
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7103" t="n">
+        <v>7102</v>
+      </c>
+    </row>
+    <row r="7104">
+      <c r="A7104" t="inlineStr">
+        <is>
+          <t>spending reductions</t>
+        </is>
+      </c>
+      <c r="B7104" t="n">
+        <v>7103</v>
+      </c>
+    </row>
+    <row r="7105">
+      <c r="A7105" t="inlineStr">
+        <is>
+          <t>state correctional grants</t>
+        </is>
+      </c>
+      <c r="B7105" t="n">
+        <v>7104</v>
+      </c>
+    </row>
+    <row r="7106">
+      <c r="A7106" t="inlineStr">
+        <is>
+          <t>state criminal alien assistance program</t>
+        </is>
+      </c>
+      <c r="B7106" t="n">
+        <v>7105</v>
+      </c>
+    </row>
+    <row r="7107">
+      <c r="A7107" t="inlineStr">
+        <is>
+          <t>state criminal records upgrade</t>
+        </is>
+      </c>
+      <c r="B7107" t="n">
+        <v>7106</v>
+      </c>
+    </row>
+    <row r="7108">
+      <c r="A7108" t="inlineStr">
+        <is>
+          <t>state legalization impact-assistance grants
+ (including rescission)</t>
+        </is>
+      </c>
+      <c r="B7108" t="n">
+        <v>7107</v>
+      </c>
+    </row>
+    <row r="7109">
+      <c r="A7109" t="inlineStr">
+        <is>
+          <t>supplemental security income program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7109" t="n">
+        <v>7108</v>
+      </c>
+    </row>
+    <row r="7110">
+      <c r="A7110" t="inlineStr">
+        <is>
+          <t>surface transportation projects</t>
+        </is>
+      </c>
+      <c r="B7110" t="n">
+        <v>7109</v>
+      </c>
+    </row>
+    <row r="7111">
+      <c r="A7111" t="inlineStr">
+        <is>
+          <t>transitional housing loan program
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7111" t="n">
+        <v>7110</v>
+      </c>
+    </row>
+    <row r="7112">
+      <c r="A7112" t="inlineStr">
+        <is>
+          <t>treasury forfeiture fund
+ (limitation of availability of deposits)</t>
+        </is>
+      </c>
+      <c r="B7112" t="n">
+        <v>7111</v>
+      </c>
+    </row>
+    <row r="7113">
+      <c r="A7113" t="inlineStr">
+        <is>
+          <t>trust fund share of next generation high speed rail
+ (liquidation of contract authorization)
+(highway trust fund)</t>
+        </is>
+      </c>
+      <c r="B7113" t="n">
+        <v>7112</v>
+      </c>
+    </row>
+    <row r="7114">
+      <c r="A7114" t="inlineStr">
+        <is>
+          <t>trust fund share of next generation rail technology development
+ (highway trust fund)</t>
+        </is>
+      </c>
+      <c r="B7114" t="n">
+        <v>7113</v>
+      </c>
+    </row>
+    <row r="7115">
+      <c r="A7115" t="inlineStr">
+        <is>
+          <t>under secretary for technology/office of technology policy</t>
+        </is>
+      </c>
+      <c r="B7115" t="n">
+        <v>7114</v>
+      </c>
+    </row>
+    <row r="7116">
+      <c r="A7116" t="inlineStr">
+        <is>
+          <t>uranium supply and enrichment activities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7116" t="n">
+        <v>7115</v>
+      </c>
+    </row>
+    <row r="7117">
+      <c r="A7117" t="inlineStr">
+        <is>
+          <t>veterans health administration
+ (by transfer)</t>
+        </is>
+      </c>
+      <c r="B7117" t="n">
+        <v>7116</v>
+      </c>
+    </row>
+    <row r="7118">
+      <c r="A7118" t="inlineStr">
+        <is>
+          <t>vocational rehabilitation loans program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7118" t="n">
+        <v>7117</v>
+      </c>
+    </row>
+    <row r="7119">
+      <c r="A7119" t="inlineStr">
+        <is>
+          <t>water and sewer enterprise fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7119" t="n">
+        <v>7118</v>
+      </c>
+    </row>
+    <row r="7120">
+      <c r="A7120" t="inlineStr">
+        <is>
+          <t>water infrastructure/state revolving fund</t>
+        </is>
+      </c>
+      <c r="B7120" t="n">
+        <v>7119</v>
+      </c>
+    </row>
+    <row r="7121">
+      <c r="A7121" t="inlineStr">
+        <is>
+          <t>water infrastructure/state revolving funds</t>
+        </is>
+      </c>
+      <c r="B7121" t="n">
+        <v>7120</v>
+      </c>
+    </row>
+    <row r="7122">
+      <c r="A7122" t="inlineStr">
+        <is>
+          <t>water infrastructure/state revolving funds
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7122" t="n">
+        <v>7121</v>
+      </c>
+    </row>
+    <row r="7123">
+      <c r="A7123" t="inlineStr">
+        <is>
+          <t>watershed and flood prevention operations
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7123" t="n">
+        <v>7122</v>
+      </c>
+    </row>
+    <row r="7124">
+      <c r="A7124" t="inlineStr">
+        <is>
+          <t>wetlands reserve program
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7124" t="n">
+        <v>7123</v>
+      </c>
+    </row>
+    <row r="7125">
+      <c r="A7125" t="inlineStr">
+        <is>
+          <t>youthbuild program
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7125" t="n">
+        <v>7124</v>
+      </c>
+    </row>
+    <row r="7126">
+      <c r="A7126" t="inlineStr">
+        <is>
+          <t>acquisition, construction, improvements, and related expenses
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7126" t="n">
+        <v>7125</v>
+      </c>
+    </row>
+    <row r="7127">
+      <c r="A7127" t="inlineStr">
+        <is>
+          <t>administration of territories
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7127" t="n">
+        <v>7126</v>
+      </c>
+    </row>
+    <row r="7128">
+      <c r="A7128" t="inlineStr">
+        <is>
+          <t>administrative provision—internal revenue service</t>
+        </is>
+      </c>
+      <c r="B7128" t="n">
+        <v>7127</v>
+      </c>
+    </row>
+    <row r="7129">
+      <c r="A7129" t="inlineStr">
+        <is>
+          <t>agency for international development
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7129" t="n">
+        <v>7128</v>
+      </c>
+    </row>
+    <row r="7130">
+      <c r="A7130" t="inlineStr">
+        <is>
+          <t>aging services programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7130" t="n">
+        <v>7129</v>
+      </c>
+    </row>
+    <row r="7131">
+      <c r="A7131" t="inlineStr">
+        <is>
+          <t>aircraft procurement, air force
+ (rescissions and transfer)</t>
+        </is>
+      </c>
+      <c r="B7131" t="n">
+        <v>7130</v>
+      </c>
+    </row>
+    <row r="7132">
+      <c r="A7132" t="inlineStr">
+        <is>
+          <t>alcohol fuels credit guarantee program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7132" t="n">
+        <v>7131</v>
+      </c>
+    </row>
+    <row r="7133">
+      <c r="A7133" t="inlineStr">
+        <is>
+          <t>alternative agricultural research and commercialization
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7133" t="n">
+        <v>7132</v>
+      </c>
+    </row>
+    <row r="7134">
+      <c r="A7134" t="inlineStr">
+        <is>
+          <t>archives facilities and presidential libraries</t>
+        </is>
+      </c>
+      <c r="B7134" t="n">
+        <v>7133</v>
+      </c>
+    </row>
+    <row r="7135">
+      <c r="A7135" t="inlineStr">
+        <is>
+          <t>arms control and disarmament activities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7135" t="n">
+        <v>7134</v>
+      </c>
+    </row>
+    <row r="7136">
+      <c r="A7136" t="inlineStr">
+        <is>
+          <t>assistance for the renewal of expiring section 8 subsidy contracts
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7136" t="n">
+        <v>7135</v>
+      </c>
+    </row>
+    <row r="7137">
+      <c r="A7137" t="inlineStr">
+        <is>
+          <t>bilingual and immigrant education
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7137" t="n">
+        <v>7136</v>
+      </c>
+    </row>
+    <row r="7138">
+      <c r="A7138" t="inlineStr">
+        <is>
+          <t>bureau of the public debt
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7138" t="n">
+        <v>7137</v>
+      </c>
+    </row>
+    <row r="7139">
+      <c r="A7139" t="inlineStr">
+        <is>
+          <t>bureau of transportation statistics</t>
+        </is>
+      </c>
+      <c r="B7139" t="n">
+        <v>7138</v>
+      </c>
+    </row>
+    <row r="7140">
+      <c r="A7140" t="inlineStr">
+        <is>
+          <t>capitol power plant
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7140" t="n">
+        <v>7139</v>
+      </c>
+    </row>
+    <row r="7141">
+      <c r="A7141" t="inlineStr">
+        <is>
+          <t>children and families services programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7141" t="n">
+        <v>7140</v>
+      </c>
+    </row>
+    <row r="7142">
+      <c r="A7142" t="inlineStr">
+        <is>
+          <t>college housing and academic facilities loans program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7142" t="n">
+        <v>7141</v>
+      </c>
+    </row>
+    <row r="7143">
+      <c r="A7143" t="inlineStr">
+        <is>
+          <t>community development financial institutions fund</t>
+        </is>
+      </c>
+      <c r="B7143" t="n">
+        <v>7142</v>
+      </c>
+    </row>
+    <row r="7144">
+      <c r="A7144" t="inlineStr">
+        <is>
+          <t>community facility loans program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7144" t="n">
+        <v>7143</v>
+      </c>
+    </row>
+    <row r="7145">
+      <c r="A7145" t="inlineStr">
+        <is>
+          <t>community service employment for older americans
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7145" t="n">
+        <v>7144</v>
+      </c>
+    </row>
+    <row r="7146">
+      <c r="A7146" t="inlineStr">
+        <is>
+          <t>community services block grant
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7146" t="n">
+        <v>7145</v>
+      </c>
+    </row>
+    <row r="7147">
+      <c r="A7147" t="inlineStr">
+        <is>
+          <t>compact of free association
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7147" t="n">
+        <v>7146</v>
+      </c>
+    </row>
+    <row r="7148">
+      <c r="A7148" t="inlineStr">
+        <is>
+          <t>congregate services
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7148" t="n">
+        <v>7147</v>
+      </c>
+    </row>
+    <row r="7149">
+      <c r="A7149" t="inlineStr">
+        <is>
+          <t>congressional printing and binding
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7149" t="n">
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="7150">
+      <c r="A7150" t="inlineStr">
+        <is>
+          <t>consolidated farm service agency</t>
+        </is>
+      </c>
+      <c r="B7150" t="n">
+        <v>7149</v>
+      </c>
+    </row>
+    <row r="7151">
+      <c r="A7151" t="inlineStr">
+        <is>
+          <t>construction and access
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7151" t="n">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="7152">
+      <c r="A7152" t="inlineStr">
+        <is>
+          <t>construction and improvements, national zoological park
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7152" t="n">
+        <v>7151</v>
+      </c>
+    </row>
+    <row r="7153">
+      <c r="A7153" t="inlineStr">
+        <is>
+          <t>construction of research facilities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7153" t="n">
+        <v>7152</v>
+      </c>
+    </row>
+    <row r="7154">
+      <c r="A7154" t="inlineStr">
+        <is>
+          <t>construction, major projects
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7154" t="n">
+        <v>7153</v>
+      </c>
+    </row>
+    <row r="7155">
+      <c r="A7155" t="inlineStr">
+        <is>
+          <t>contribution to the african development fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7155" t="n">
+        <v>7154</v>
+      </c>
+    </row>
+    <row r="7156">
+      <c r="A7156" t="inlineStr">
+        <is>
+          <t>contribution to the international development association
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7156" t="n">
+        <v>7155</v>
+      </c>
+    </row>
+    <row r="7157">
+      <c r="A7157" t="inlineStr">
+        <is>
+          <t>contributions for international peacekeeping activities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7157" t="n">
+        <v>7156</v>
+      </c>
+    </row>
+    <row r="7158">
+      <c r="A7158" t="inlineStr">
+        <is>
+          <t>corporation for public broadcasting
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7158" t="n">
+        <v>7157</v>
+      </c>
+    </row>
+    <row r="7159">
+      <c r="A7159" t="inlineStr">
+        <is>
+          <t>corps of engineers—civil
+ flood control, mississippi river and tributaries, arkansas, illinois, kentucky, louisiana, mississippi, missouri, and tennessee</t>
+        </is>
+      </c>
+      <c r="B7159" t="n">
+        <v>7158</v>
+      </c>
+    </row>
+    <row r="7160">
+      <c r="A7160" t="inlineStr">
+        <is>
+          <t>debt restructuring under the enterprise for the americas initiative
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7160" t="n">
+        <v>7159</v>
+      </c>
+    </row>
+    <row r="7161">
+      <c r="A7161" t="inlineStr">
+        <is>
+          <t>defense production act purchases
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7161" t="n">
+        <v>7160</v>
+      </c>
+    </row>
+    <row r="7162">
+      <c r="A7162" t="inlineStr">
+        <is>
+          <t>development assistance fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7162" t="n">
+        <v>7161</v>
+      </c>
+    </row>
+    <row r="7163">
+      <c r="A7163" t="inlineStr">
+        <is>
+          <t>development fund for africa
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7163" t="n">
+        <v>7162</v>
+      </c>
+    </row>
+    <row r="7164">
+      <c r="A7164" t="inlineStr">
+        <is>
+          <t>diplomatic and consular programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7164" t="n">
+        <v>7163</v>
+      </c>
+    </row>
+    <row r="7165">
+      <c r="A7165" t="inlineStr">
+        <is>
+          <t>disaster relief emergency contingency fund</t>
+        </is>
+      </c>
+      <c r="B7165" t="n">
+        <v>7164</v>
+      </c>
+    </row>
+    <row r="7166">
+      <c r="A7166" t="inlineStr">
+        <is>
+          <t>discretionary grants
+ (limitation on obligations)
+(highway trust fund)
+(rescissions of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B7166" t="n">
+        <v>7165</v>
+      </c>
+    </row>
+    <row r="7167">
+      <c r="A7167" t="inlineStr">
+        <is>
+          <t>disease control, research, and training
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7167" t="n">
+        <v>7166</v>
+      </c>
+    </row>
+    <row r="7168">
+      <c r="A7168" t="inlineStr">
+        <is>
+          <t>distance learning and medical link grants</t>
+        </is>
+      </c>
+      <c r="B7168" t="n">
+        <v>7167</v>
+      </c>
+    </row>
+    <row r="7169">
+      <c r="A7169" t="inlineStr">
+        <is>
+          <t>drug courts
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7169" t="n">
+        <v>7168</v>
+      </c>
+    </row>
+    <row r="7170">
+      <c r="A7170" t="inlineStr">
+        <is>
+          <t>dual benefits payments account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7170" t="n">
+        <v>7169</v>
+      </c>
+    </row>
+    <row r="7171">
+      <c r="A7171" t="inlineStr">
+        <is>
+          <t>economic development assistance programs
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7171" t="n">
+        <v>7170</v>
+      </c>
+    </row>
+    <row r="7172">
+      <c r="A7172" t="inlineStr">
+        <is>
+          <t>education for the disadvantaged
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7172" t="n">
+        <v>7171</v>
+      </c>
+    </row>
+    <row r="7173">
+      <c r="A7173" t="inlineStr">
+        <is>
+          <t>education reform
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7173" t="n">
+        <v>7172</v>
+      </c>
+    </row>
+    <row r="7174">
+      <c r="A7174" t="inlineStr">
+        <is>
+          <t>education research, statistics, and improvement
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7174" t="n">
+        <v>7173</v>
+      </c>
+    </row>
+    <row r="7175">
+      <c r="A7175" t="inlineStr">
+        <is>
+          <t>eligibility of state and local public housing units for comprehensive grants</t>
+        </is>
+      </c>
+      <c r="B7175" t="n">
+        <v>7174</v>
+      </c>
+    </row>
+    <row r="7176">
+      <c r="A7176" t="inlineStr">
+        <is>
+          <t>energy conservation
+ (rescissions)</t>
+        </is>
+      </c>
+      <c r="B7176" t="n">
+        <v>7175</v>
+      </c>
+    </row>
+    <row r="7177">
+      <c r="A7177" t="inlineStr">
+        <is>
+          <t>environmental compliance and restoration
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7177" t="n">
+        <v>7176</v>
+      </c>
+    </row>
+    <row r="7178">
+      <c r="A7178" t="inlineStr">
+        <is>
+          <t>environmental restoration, defense
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7178" t="n">
+        <v>7177</v>
+      </c>
+    </row>
+    <row r="7179">
+      <c r="A7179" t="inlineStr">
+        <is>
+          <t>fdic affordable housing program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7179" t="n">
+        <v>7178</v>
+      </c>
+    </row>
+    <row r="7180">
+      <c r="A7180" t="inlineStr">
+        <is>
+          <t>federal buildings fund
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7180" t="n">
+        <v>7179</v>
+      </c>
+    </row>
+    <row r="7181">
+      <c r="A7181" t="inlineStr">
+        <is>
+          <t>federal direct student loan program</t>
+        </is>
+      </c>
+      <c r="B7181" t="n">
+        <v>7180</v>
+      </c>
+    </row>
+    <row r="7182">
+      <c r="A7182" t="inlineStr">
+        <is>
+          <t>federal-aid highways
+ (limitation on obligations)
+(highway trust fund)
+(rescissions of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B7182" t="n">
+        <v>7181</v>
+      </c>
+    </row>
+    <row r="7183">
+      <c r="A7183" t="inlineStr">
+        <is>
+          <t>fees of jurors and commissioners
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7183" t="n">
+        <v>7182</v>
+      </c>
+    </row>
+    <row r="7184">
+      <c r="A7184" t="inlineStr">
+        <is>
+          <t>flexible subsidy fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7184" t="n">
+        <v>7183</v>
+      </c>
+    </row>
+    <row r="7185">
+      <c r="A7185" t="inlineStr">
+        <is>
+          <t>food for progress</t>
+        </is>
+      </c>
+      <c r="B7185" t="n">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="7186">
+      <c r="A7186" t="inlineStr">
+        <is>
+          <t>foreign agricultural service
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7186" t="n">
+        <v>7185</v>
+      </c>
+    </row>
+    <row r="7187">
+      <c r="A7187" t="inlineStr">
+        <is>
+          <t>forest research
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7187" t="n">
+        <v>7186</v>
+      </c>
+    </row>
+    <row r="7188">
+      <c r="A7188" t="inlineStr">
+        <is>
+          <t>general provisions
+ (including rescissions)</t>
+        </is>
+      </c>
+      <c r="B7188" t="n">
+        <v>7187</v>
+      </c>
+    </row>
+    <row r="7189">
+      <c r="A7189" t="inlineStr">
+        <is>
+          <t>general provisions—department of the treasury</t>
+        </is>
+      </c>
+      <c r="B7189" t="n">
+        <v>7188</v>
+      </c>
+    </row>
+    <row r="7190">
+      <c r="A7190" t="inlineStr">
+        <is>
+          <t>general provisions—office of personnel management</t>
+        </is>
+      </c>
+      <c r="B7190" t="n">
+        <v>7189</v>
+      </c>
+    </row>
+    <row r="7191">
+      <c r="A7191" t="inlineStr">
+        <is>
+          <t>goes satellite contingency fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7191" t="n">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="7192">
+      <c r="A7192" t="inlineStr">
+        <is>
+          <t>grants and administration
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7192" t="n">
+        <v>7191</v>
+      </c>
+    </row>
+    <row r="7193">
+      <c r="A7193" t="inlineStr">
+        <is>
+          <t>grants to the national railroad passenger corporation
+ (including transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7193" t="n">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="7194">
+      <c r="A7194" t="inlineStr">
+        <is>
+          <t>health care policy and research
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7194" t="n">
+        <v>7193</v>
+      </c>
+    </row>
+    <row r="7195">
+      <c r="A7195" t="inlineStr">
+        <is>
+          <t>health resources and services
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7195" t="n">
+        <v>7194</v>
+      </c>
+    </row>
+    <row r="7196">
+      <c r="A7196" t="inlineStr">
+        <is>
+          <t>higher education
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7196" t="n">
+        <v>7195</v>
+      </c>
+    </row>
+    <row r="7197">
+      <c r="A7197" t="inlineStr">
+        <is>
+          <t>homeless assistance grants
+ (deferral)</t>
+        </is>
+      </c>
+      <c r="B7197" t="n">
+        <v>7196</v>
+      </c>
+    </row>
+    <row r="7198">
+      <c r="A7198" t="inlineStr">
+        <is>
+          <t>housing counseling assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7198" t="n">
+        <v>7197</v>
+      </c>
+    </row>
+    <row r="7199">
+      <c r="A7199" t="inlineStr">
+        <is>
+          <t>howard university
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7199" t="n">
+        <v>7198</v>
+      </c>
+    </row>
+    <row r="7200">
+      <c r="A7200" t="inlineStr">
+        <is>
+          <t>independent agencies
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7200" t="n">
+        <v>7199</v>
+      </c>
+    </row>
+    <row r="7201">
+      <c r="A7201" t="inlineStr">
+        <is>
+          <t>indian direct loan program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7201" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="7202">
+      <c r="A7202" t="inlineStr">
+        <is>
+          <t>indian education
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7202" t="n">
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="7203">
+      <c r="A7203" t="inlineStr">
+        <is>
+          <t>information infrastructure grants
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7203" t="n">
+        <v>7202</v>
+      </c>
+    </row>
+    <row r="7204">
+      <c r="A7204" t="inlineStr">
+        <is>
+          <t>intermediate-term export credit</t>
+        </is>
+      </c>
+      <c r="B7204" t="n">
+        <v>7203</v>
+      </c>
+    </row>
+    <row r="7205">
+      <c r="A7205" t="inlineStr">
+        <is>
+          <t>international forestry
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7205" t="n">
+        <v>7204</v>
+      </c>
+    </row>
+    <row r="7206">
+      <c r="A7206" t="inlineStr">
+        <is>
+          <t>international organizations and programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7206" t="n">
+        <v>7205</v>
+      </c>
+    </row>
+    <row r="7207">
+      <c r="A7207" t="inlineStr">
+        <is>
+          <t>joint committee on printing
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7207" t="n">
+        <v>7206</v>
+      </c>
+    </row>
+    <row r="7208">
+      <c r="A7208" t="inlineStr">
+        <is>
+          <t>joint economic committee
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7208" t="n">
+        <v>7207</v>
+      </c>
+    </row>
+    <row r="7209">
+      <c r="A7209" t="inlineStr">
+        <is>
+          <t>kaho’olawe island conveyance, remediation, and environmental restoration trust fund</t>
+        </is>
+      </c>
+      <c r="B7209" t="n">
+        <v>7208</v>
+      </c>
+    </row>
+    <row r="7210">
+      <c r="A7210" t="inlineStr">
+        <is>
+          <t>land acquisition
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7210" t="n">
+        <v>7209</v>
+      </c>
+    </row>
+    <row r="7211">
+      <c r="A7211" t="inlineStr">
+        <is>
+          <t>land acquisition and state assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7211" t="n">
+        <v>7210</v>
+      </c>
+    </row>
+    <row r="7212">
+      <c r="A7212" t="inlineStr">
+        <is>
+          <t>limitation on general operating expenses
+ (rescission of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B7212" t="n">
+        <v>7211</v>
+      </c>
+    </row>
+    <row r="7213">
+      <c r="A7213" t="inlineStr">
+        <is>
+          <t>limitations on availability of revenue
+ (including rescission)</t>
+        </is>
+      </c>
+      <c r="B7213" t="n">
+        <v>7212</v>
+      </c>
+    </row>
+    <row r="7214">
+      <c r="A7214" t="inlineStr">
+        <is>
+          <t>limitations on the availability of revenue
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7214" t="n">
+        <v>7213</v>
+      </c>
+    </row>
+    <row r="7215">
+      <c r="A7215" t="inlineStr">
+        <is>
+          <t>local rail freight assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7215" t="n">
+        <v>7214</v>
+      </c>
+    </row>
+    <row r="7216">
+      <c r="A7216" t="inlineStr">
+        <is>
+          <t>local technical assistance and planning grants
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7216" t="n">
+        <v>7215</v>
+      </c>
+    </row>
+    <row r="7217">
+      <c r="A7217" t="inlineStr">
+        <is>
+          <t>low income home energy assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7217" t="n">
+        <v>7216</v>
+      </c>
+    </row>
+    <row r="7218">
+      <c r="A7218" t="inlineStr">
+        <is>
+          <t>miscellaneous highway demonstration projects
+ (highway trust fund)
+(rescission)</t>
+        </is>
+      </c>
+      <c r="B7218" t="n">
+        <v>7217</v>
+      </c>
+    </row>
+    <row r="7219">
+      <c r="A7219" t="inlineStr">
+        <is>
+          <t>mission support
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7219" t="n">
+        <v>7218</v>
+      </c>
+    </row>
+    <row r="7220">
+      <c r="A7220" t="inlineStr">
+        <is>
+          <t>multilateral economic assistance
+ funds appropriated to the president</t>
+        </is>
+      </c>
+      <c r="B7220" t="n">
+        <v>7219</v>
+      </c>
+    </row>
+    <row r="7221">
+      <c r="A7221" t="inlineStr">
+        <is>
+          <t>national aeronautical facilities</t>
+        </is>
+      </c>
+      <c r="B7221" t="n">
+        <v>7220</v>
+      </c>
+    </row>
+    <row r="7222">
+      <c r="A7222" t="inlineStr">
+        <is>
+          <t>national and community service programs operating expenses
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7222" t="n">
+        <v>7221</v>
+      </c>
+    </row>
+    <row r="7223">
+      <c r="A7223" t="inlineStr">
+        <is>
+          <t>national bankruptcy review commission
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7223" t="n">
+        <v>7222</v>
+      </c>
+    </row>
+    <row r="7224">
+      <c r="A7224" t="inlineStr">
+        <is>
+          <t>national center for research resources
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7224" t="n">
+        <v>7223</v>
+      </c>
+    </row>
+    <row r="7225">
+      <c r="A7225" t="inlineStr">
+        <is>
+          <t>national flood insurance fund
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7225" t="n">
+        <v>7224</v>
+      </c>
+    </row>
+    <row r="7226">
+      <c r="A7226" t="inlineStr">
+        <is>
+          <t>national guard and reserve equipment
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7226" t="n">
+        <v>7225</v>
+      </c>
+    </row>
+    <row r="7227">
+      <c r="A7227" t="inlineStr">
+        <is>
+          <t>national homeownership trust demonstration program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7227" t="n">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="7228">
+      <c r="A7228" t="inlineStr">
+        <is>
+          <t>national magnetic levitation prototype development program
+ (highway trust fund)
+(rescission of contract authorization)</t>
+        </is>
+      </c>
+      <c r="B7228" t="n">
+        <v>7227</v>
+      </c>
+    </row>
+    <row r="7229">
+      <c r="A7229" t="inlineStr">
+        <is>
+          <t>national security education trust fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7229" t="n">
+        <v>7228</v>
+      </c>
+    </row>
+    <row r="7230">
+      <c r="A7230" t="inlineStr">
+        <is>
+          <t>nehemiah housing opportunities fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7230" t="n">
+        <v>7229</v>
+      </c>
+    </row>
+    <row r="7231">
+      <c r="A7231" t="inlineStr">
+        <is>
+          <t>ntis revolving fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7231" t="n">
+        <v>7230</v>
+      </c>
+    </row>
+    <row r="7232">
+      <c r="A7232" t="inlineStr">
+        <is>
+          <t>office of the administrator
+ (transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7232" t="n">
+        <v>7231</v>
+      </c>
+    </row>
+    <row r="7233">
+      <c r="A7233" t="inlineStr">
+        <is>
+          <t>office of the assistant secretary for health
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7233" t="n">
+        <v>7232</v>
+      </c>
+    </row>
+    <row r="7234">
+      <c r="A7234" t="inlineStr">
+        <is>
+          <t>office of the secretary
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7234" t="n">
+        <v>7233</v>
+      </c>
+    </row>
+    <row r="7235">
+      <c r="A7235" t="inlineStr">
+        <is>
+          <t>office of the under secretary for rural economic and community development</t>
+        </is>
+      </c>
+      <c r="B7235" t="n">
+        <v>7234</v>
+      </c>
+    </row>
+    <row r="7236">
+      <c r="A7236" t="inlineStr">
+        <is>
+          <t>operating expenses of the agency for international development
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7236" t="n">
+        <v>7235</v>
+      </c>
+    </row>
+    <row r="7237">
+      <c r="A7237" t="inlineStr">
+        <is>
+          <t>operation and maintenance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7237" t="n">
+        <v>7236</v>
+      </c>
+    </row>
+    <row r="7238">
+      <c r="A7238" t="inlineStr">
+        <is>
+          <t>operation and maintenance, army national guard
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7238" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="7239">
+      <c r="A7239" t="inlineStr">
+        <is>
+          <t>operation and maintenance, army reserve
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7239" t="n">
+        <v>7238</v>
+      </c>
+    </row>
+    <row r="7240">
+      <c r="A7240" t="inlineStr">
+        <is>
+          <t>operation of indian programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7240" t="n">
+        <v>7239</v>
+      </c>
+    </row>
+    <row r="7241">
+      <c r="A7241" t="inlineStr">
+        <is>
+          <t>operations, research and facilities
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7241" t="n">
+        <v>7240</v>
+      </c>
+    </row>
+    <row r="7242">
+      <c r="A7242" t="inlineStr">
+        <is>
+          <t>payment to the legal services corporation
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7242" t="n">
+        <v>7241</v>
+      </c>
+    </row>
+    <row r="7243">
+      <c r="A7243" t="inlineStr">
+        <is>
+          <t>payments in lieu of taxes
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7243" t="n">
+        <v>7242</v>
+      </c>
+    </row>
+    <row r="7244">
+      <c r="A7244" t="inlineStr">
+        <is>
+          <t>peacekeeping operations
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7244" t="n">
+        <v>7243</v>
+      </c>
+    </row>
+    <row r="7245">
+      <c r="A7245" t="inlineStr">
+        <is>
+          <t>pennsylvania station redevelopment project
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7245" t="n">
+        <v>7244</v>
+      </c>
+    </row>
+    <row r="7246">
+      <c r="A7246" t="inlineStr">
+        <is>
+          <t>policy research
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7246" t="n">
+        <v>7245</v>
+      </c>
+    </row>
+    <row r="7247">
+      <c r="A7247" t="inlineStr">
+        <is>
+          <t>population, development assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7247" t="n">
+        <v>7246</v>
+      </c>
+    </row>
+    <row r="7248">
+      <c r="A7248" t="inlineStr">
+        <is>
+          <t>port safety development</t>
+        </is>
+      </c>
+      <c r="B7248" t="n">
+        <v>7247</v>
+      </c>
+    </row>
+    <row r="7249">
+      <c r="A7249" t="inlineStr">
+        <is>
+          <t>power marketing administrations
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7249" t="n">
+        <v>7248</v>
+      </c>
+    </row>
+    <row r="7250">
+      <c r="A7250" t="inlineStr">
+        <is>
+          <t>program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7250" t="n">
+        <v>7249</v>
+      </c>
+    </row>
+    <row r="7251">
+      <c r="A7251" t="inlineStr">
+        <is>
+          <t>public law 480 program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7251" t="n">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="7252">
+      <c r="A7252" t="inlineStr">
+        <is>
+          <t>radio free asia
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7252" t="n">
+        <v>7251</v>
+      </c>
+    </row>
+    <row r="7253">
+      <c r="A7253" t="inlineStr">
+        <is>
+          <t>repair, restoration and renovation of buildings
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7253" t="n">
+        <v>7252</v>
+      </c>
+    </row>
+    <row r="7254">
+      <c r="A7254" t="inlineStr">
+        <is>
+          <t>rescission</t>
+        </is>
+      </c>
+      <c r="B7254" t="n">
+        <v>7253</v>
+      </c>
+    </row>
+    <row r="7255">
+      <c r="A7255" t="inlineStr">
+        <is>
+          <t>research, engineering, and development
+ (airport and airway trust fund)
+(rescission)</t>
+        </is>
+      </c>
+      <c r="B7255" t="n">
+        <v>7254</v>
+      </c>
+    </row>
+    <row r="7256">
+      <c r="A7256" t="inlineStr">
+        <is>
+          <t>research, inventories, and surveys
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7256" t="n">
+        <v>7255</v>
+      </c>
+    </row>
+    <row r="7257">
+      <c r="A7257" t="inlineStr">
+        <is>
+          <t>royalty and offshore minerals management
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7257" t="n">
+        <v>7256</v>
+      </c>
+    </row>
+    <row r="7258">
+      <c r="A7258" t="inlineStr">
+        <is>
+          <t>rural business and cooperative development service</t>
+        </is>
+      </c>
+      <c r="B7258" t="n">
+        <v>7257</v>
+      </c>
+    </row>
+    <row r="7259">
+      <c r="A7259" t="inlineStr">
+        <is>
+          <t>rural business and industry loans program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7259" t="n">
+        <v>7258</v>
+      </c>
+    </row>
+    <row r="7260">
+      <c r="A7260" t="inlineStr">
+        <is>
+          <t>rural electrification and telephone loans program account
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7260" t="n">
+        <v>7259</v>
+      </c>
+    </row>
+    <row r="7261">
+      <c r="A7261" t="inlineStr">
+        <is>
+          <t>rural electrification and telephone loans program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7261" t="n">
+        <v>7260</v>
+      </c>
+    </row>
+    <row r="7262">
+      <c r="A7262" t="inlineStr">
+        <is>
+          <t>rural housing and community development service</t>
+        </is>
+      </c>
+      <c r="B7262" t="n">
+        <v>7261</v>
+      </c>
+    </row>
+    <row r="7263">
+      <c r="A7263" t="inlineStr">
+        <is>
+          <t>rural housing insurance fund program account
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7263" t="n">
+        <v>7262</v>
+      </c>
+    </row>
+    <row r="7264">
+      <c r="A7264" t="inlineStr">
+        <is>
+          <t>salaries and expenses
+ (rescission and transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7264" t="n">
+        <v>7263</v>
+      </c>
+    </row>
+    <row r="7265">
+      <c r="A7265" t="inlineStr">
+        <is>
+          <t>school improvement programs
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7265" t="n">
+        <v>7264</v>
+      </c>
+    </row>
+    <row r="7266">
+      <c r="A7266" t="inlineStr">
+        <is>
+          <t>science, aeronautics and technology
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7266" t="n">
+        <v>7265</v>
+      </c>
+    </row>
+    <row r="7267">
+      <c r="A7267" t="inlineStr">
+        <is>
+          <t>senate office buildings
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7267" t="n">
+        <v>7266</v>
+      </c>
+    </row>
+    <row r="7268">
+      <c r="A7268" t="inlineStr">
+        <is>
+          <t>settlements and awards reserve</t>
+        </is>
+      </c>
+      <c r="B7268" t="n">
+        <v>7267</v>
+      </c>
+    </row>
+    <row r="7269">
+      <c r="A7269" t="inlineStr">
+        <is>
+          <t>space flight, control and data communications
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7269" t="n">
+        <v>7268</v>
+      </c>
+    </row>
+    <row r="7270">
+      <c r="A7270" t="inlineStr">
+        <is>
+          <t>special forfeiture fund
+ (including rescission and transfer of funds)</t>
+        </is>
+      </c>
+      <c r="B7270" t="n">
+        <v>7269</v>
+      </c>
+    </row>
+    <row r="7271">
+      <c r="A7271" t="inlineStr">
+        <is>
+          <t>special supplemental food program for women, infants, and children (wic)
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7271" t="n">
+        <v>7270</v>
+      </c>
+    </row>
+    <row r="7272">
+      <c r="A7272" t="inlineStr">
+        <is>
+          <t>special supplemental nutrition program for women, infants, and children (wic)
+ (including transfers of funds)</t>
+        </is>
+      </c>
+      <c r="B7272" t="n">
+        <v>7271</v>
+      </c>
+    </row>
+    <row r="7273">
+      <c r="A7273" t="inlineStr">
+        <is>
+          <t>state legalization impact-assistance grants
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7273" t="n">
+        <v>7272</v>
+      </c>
+    </row>
+    <row r="7274">
+      <c r="A7274" t="inlineStr">
+        <is>
+          <t>state unemployment insurance and employment service operations
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7274" t="n">
+        <v>7273</v>
+      </c>
+    </row>
+    <row r="7275">
+      <c r="A7275" t="inlineStr">
+        <is>
+          <t>student financial assistance
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7275" t="n">
+        <v>7274</v>
+      </c>
+    </row>
+    <row r="7276">
+      <c r="A7276" t="inlineStr">
+        <is>
+          <t>tennessee valley authority fund
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7276" t="n">
+        <v>7275</v>
+      </c>
+    </row>
+    <row r="7277">
+      <c r="A7277" t="inlineStr">
+        <is>
+          <t>trade and development agency
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7277" t="n">
+        <v>7276</v>
+      </c>
+    </row>
+    <row r="7278">
+      <c r="A7278" t="inlineStr">
+        <is>
+          <t>training and employment services
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7278" t="n">
+        <v>7277</v>
+      </c>
+    </row>
+    <row r="7279">
+      <c r="A7279" t="inlineStr">
+        <is>
+          <t>transit planning and research
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7279" t="n">
+        <v>7278</v>
+      </c>
+    </row>
+    <row r="7280">
+      <c r="A7280" t="inlineStr">
+        <is>
+          <t>treasury buildings and annex repair and restoration</t>
+        </is>
+      </c>
+      <c r="B7280" t="n">
+        <v>7279</v>
+      </c>
+    </row>
+    <row r="7281">
+      <c r="A7281" t="inlineStr">
+        <is>
+          <t>treasury forfeiture fund</t>
+        </is>
+      </c>
+      <c r="B7281" t="n">
+        <v>7280</v>
+      </c>
+    </row>
+    <row r="7282">
+      <c r="A7282" t="inlineStr">
+        <is>
+          <t>trust territory of the pacific islands
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7282" t="n">
+        <v>7281</v>
+      </c>
+    </row>
+    <row r="7283">
+      <c r="A7283" t="inlineStr">
+        <is>
+          <t>united states custom service</t>
+        </is>
+      </c>
+      <c r="B7283" t="n">
+        <v>7282</v>
+      </c>
+    </row>
+    <row r="7284">
+      <c r="A7284" t="inlineStr">
+        <is>
+          <t>united states fish and wildlife service
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7284" t="n">
+        <v>7283</v>
+      </c>
+    </row>
+    <row r="7285">
+      <c r="A7285" t="inlineStr">
+        <is>
+          <t>youthbuild program
+ (rescission)</t>
+        </is>
+      </c>
+      <c r="B7285" t="n">
+        <v>7284</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
